--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>0</v>
+        <v>155.52</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>0 de 23</t>
+          <t>1 de 23</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2039,7 +2039,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2371,7 +2371,7 @@
         <v>5296.63</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0</v>
+        <v>155.52</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>6000</v>
@@ -2712,7 +2712,7 @@
         <v>59467.53</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>912.4</v>
+        <v>1067.92</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>1396.8</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
@@ -1188,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>261</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>155.52</v>
+        <v>3019.68</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -1296,7 +1296,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>438.21</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0</v>
+        <v>4661.12</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -1946,52 +1946,52 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
+          <t>1 de 23</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>1 de 23</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
           <t>0 de 23</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>0 de 23</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>1 de 23</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>1 de 23</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>0 de 23</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>0 de 23</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>1 de 23</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>0 de 23</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>0 de 23</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>0 de 23</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>0 de 23</t>
-        </is>
-      </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>1 de 23</t>
+          <t>2 de 23</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2039,7 +2039,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2182,7 +2182,7 @@
         <v>84.59</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0</v>
+        <v>1396.8</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>5000</v>
@@ -2371,7 +2371,7 @@
         <v>5296.63</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>155.52</v>
+        <v>3280.68</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>6000</v>
@@ -2425,7 +2425,7 @@
         <v>6009.13</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0</v>
+        <v>438.21</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>6500</v>
@@ -2614,7 +2614,7 @@
         <v>-496.35</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0</v>
+        <v>4661.12</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0</v>
@@ -2712,7 +2712,7 @@
         <v>59467.53</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1067.92</v>
+        <v>10689.21</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>
@@ -2729,14 +2729,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -2784,13 +2784,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>129.6</v>
+        <v>136.08</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>129.6</v>
+        <v>136.08</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>0</v>
@@ -2808,16 +2808,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2564</v>
+        <v>2183</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>9912.969999999999</v>
+        <v>1396.8</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-7348.969999999999</v>
+        <v>786.2</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>3.866212948517941</v>
+        <v>0.6398534127347687</v>
       </c>
     </row>
     <row r="4">
@@ -2832,16 +2832,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>207.39</v>
+        <v>584</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>537.5</v>
+        <v>438.21</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-330.11</v>
+        <v>145.79</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.591735377790636</v>
+        <v>0.7503595890410959</v>
       </c>
     </row>
     <row r="5">
@@ -2856,13 +2856,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>86.41</v>
+        <v>172.82</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>86.41</v>
+        <v>172.82</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -2880,16 +2880,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2907.58368146026</v>
+        <v>3450</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>4053.6</v>
+        <v>908.1</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-1146.01631853974</v>
+        <v>2541.9</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.394147320968655</v>
+        <v>0.2632173913043478</v>
       </c>
     </row>
     <row r="7">
@@ -2904,16 +2904,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>383.4</v>
+        <v>347.55</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>610.4</v>
+        <v>261</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-227</v>
+        <v>86.55000000000001</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.59207094418362</v>
+        <v>0.7509710832973673</v>
       </c>
     </row>
     <row r="8">
@@ -2928,13 +2928,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>415</v>
+        <v>250</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>415</v>
+        <v>250</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -2955,10 +2955,10 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>31.3</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>-31.3</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -2976,16 +2976,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1388</v>
+        <v>728.7</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>690.28</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>697.72</v>
+        <v>728.7</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.4973198847262247</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -3000,16 +3000,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2678</v>
+        <v>467</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>3604.64</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-926.6399999999999</v>
+        <v>467</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.346019417475728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3024,16 +3024,16 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>44418</v>
+        <v>36687</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>47257.91</v>
+        <v>7653.8</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-2839.910000000003</v>
+        <v>29033.2</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1.063936016930074</v>
+        <v>0.2086243083381034</v>
       </c>
     </row>
     <row r="13">
@@ -3048,35 +3048,59 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>222.087330240682</v>
+        <v>199.8</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>222.087330240682</v>
+        <v>199.8</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SAL SOLUBLE</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>55399.47101170094</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>66667.3</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>-11267.82898829906</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>1.203392357048304</v>
+      <c r="C15" s="2" t="n">
+        <v>45565.95</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>10689.21</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>34876.74000000001</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.2345876690818473</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>0</v>
+        <v>1019.4</v>
       </c>
       <c r="R11" s="2" t="n">
         <v>0</v>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="Q25" s="4" t="inlineStr">
         <is>
-          <t>0 de 23</t>
+          <t>1 de 23</t>
         </is>
       </c>
       <c r="R25" s="4" t="inlineStr">
@@ -2344,7 +2344,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0</v>
+        <v>1019.4</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>1000</v>
@@ -2712,7 +2712,7 @@
         <v>59467.53</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>10689.21</v>
+        <v>11708.61</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>
@@ -2955,10 +2955,10 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>31.3</v>
+        <v>1050.7</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-31.3</v>
+        <v>-1050.7</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -3094,13 +3094,13 @@
         <v>45565.95</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>10689.21</v>
+        <v>11708.61</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>34876.74000000001</v>
+        <v>33857.34</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.2345876690818473</v>
+        <v>0.256959637624147</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1134,13 +1134,13 @@
         <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>45.68</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>0</v>
+        <v>759.72</v>
       </c>
       <c r="N11" s="2" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>1019.4</v>
+        <v>2061.1</v>
       </c>
       <c r="R11" s="2" t="n">
         <v>0</v>
@@ -1981,17 +1981,17 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
+          <t>1 de 23</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
           <t>0 de 23</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>0 de 23</t>
-        </is>
-      </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>2 de 23</t>
+          <t>3 de 23</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2344,7 +2344,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1019.4</v>
+        <v>2866.5</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>1000</v>
@@ -2712,7 +2712,7 @@
         <v>59467.53</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>11708.61</v>
+        <v>13555.71</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>
@@ -2735,9 +2735,9 @@
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2955,10 +2955,10 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1050.7</v>
+        <v>2092.4</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-1050.7</v>
+        <v>-2092.4</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -2979,13 +2979,13 @@
         <v>728.7</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>45.68</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>728.7</v>
+        <v>683.0200000000001</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>0.06268697680801427</v>
       </c>
     </row>
     <row r="11">
@@ -3027,13 +3027,13 @@
         <v>36687</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>7653.8</v>
+        <v>8413.52</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>29033.2</v>
+        <v>28273.48</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.2086243083381034</v>
+        <v>0.2293324610897593</v>
       </c>
     </row>
     <row r="13">
@@ -3094,13 +3094,13 @@
         <v>45565.95</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>11708.61</v>
+        <v>13555.71</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>33857.34</v>
+        <v>32010.24</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.256959637624147</v>
+        <v>0.2974964858627989</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0</v>
+        <v>2600.55</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>3 de 23</t>
+          <t>4 de 23</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2506,7 +2506,7 @@
         <v>3091.73</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>939.4</v>
+        <v>3539.95</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>1500</v>
@@ -2712,7 +2712,7 @@
         <v>59467.53</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>13555.71</v>
+        <v>16156.26</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>
@@ -2735,7 +2735,7 @@
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3027,13 +3027,13 @@
         <v>36687</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>8413.52</v>
+        <v>11014.07</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>28273.48</v>
+        <v>25672.93</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.2293324610897593</v>
+        <v>0.3002172431651539</v>
       </c>
     </row>
     <row r="13">
@@ -3094,13 +3094,13 @@
         <v>45565.95</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>13555.71</v>
+        <v>16156.26</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>32010.24</v>
+        <v>29409.69</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.2974964858627989</v>
+        <v>0.3545687075546542</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1845,7 +1845,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0</v>
+        <v>940.5</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>0</v>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>1 de 23</t>
+          <t>2 de 23</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -2668,7 +2668,7 @@
         <v>1351.47</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0</v>
+        <v>940.5</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -2712,7 +2712,7 @@
         <v>59467.53</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>16156.26</v>
+        <v>17096.76</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>
@@ -2883,13 +2883,13 @@
         <v>3450</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>908.1</v>
+        <v>1848.6</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2541.9</v>
+        <v>1601.4</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.2632173913043478</v>
+        <v>0.5358260869565217</v>
       </c>
     </row>
     <row r="7">
@@ -3094,13 +3094,13 @@
         <v>45565.95</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>16156.26</v>
+        <v>17096.76</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>29409.69</v>
+        <v>28469.19</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.3545687075546542</v>
+        <v>0.3752091199678708</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0</v>
+        <v>611.02</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -1752,7 +1752,7 @@
         <v>0</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>0</v>
+        <v>-245.32</v>
       </c>
       <c r="R21" s="2" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>4 de 23</t>
+          <t>5 de 23</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2452,7 +2452,7 @@
         <v>2701.41</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>611.02</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>6500</v>
@@ -2614,7 +2614,7 @@
         <v>-496.35</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>4661.12</v>
+        <v>4415.8</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0</v>
@@ -2712,7 +2712,7 @@
         <v>59467.53</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>17096.76</v>
+        <v>17462.46</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>
@@ -2955,10 +2955,10 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2092.4</v>
+        <v>1847.08</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-2092.4</v>
+        <v>-1847.08</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -3027,13 +3027,13 @@
         <v>36687</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>11014.07</v>
+        <v>11625.09</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>25672.93</v>
+        <v>25061.91</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.3002172431651539</v>
+        <v>0.3168721890587947</v>
       </c>
     </row>
     <row r="13">
@@ -3094,13 +3094,13 @@
         <v>45565.95</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>17096.76</v>
+        <v>17462.46</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>28469.19</v>
+        <v>28103.49</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.3752091199678708</v>
+        <v>0.3832348497068534</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>2061.1</v>
+        <v>0</v>
       </c>
       <c r="R11" s="2" t="n">
         <v>0</v>
@@ -1752,7 +1752,7 @@
         <v>0</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>-245.32</v>
+        <v>0</v>
       </c>
       <c r="R21" s="2" t="n">
         <v>0</v>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="Q25" s="4" t="inlineStr">
         <is>
-          <t>1 de 23</t>
+          <t>0 de 23</t>
         </is>
       </c>
       <c r="R25" s="4" t="inlineStr">
@@ -2729,7 +2729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -2955,10 +2955,10 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1847.08</v>
+        <v>31.3</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-1847.08</v>
+        <v>-31.3</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -2996,20 +2996,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PIEDRA SINTERIZADA</t>
+          <t>PANELES PVC Y PU</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>467</v>
+        <v>115</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>1815.78</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>467</v>
+        <v>-1700.78</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>15.78939130434783</v>
       </c>
     </row>
     <row r="12">
@@ -3020,20 +3020,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PORCELANATO</t>
+          <t>PIEDRA SINTERIZADA</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>36687</v>
+        <v>467</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>11625.09</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>25061.91</v>
+        <v>467</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.3168721890587947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3044,20 +3044,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PUERTAS DE SEGURIDAD</t>
+          <t>PORCELANATO</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>199.8</v>
+        <v>36687</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>11625.09</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>199.8</v>
+        <v>25061.91</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>0.3168721890587947</v>
       </c>
     </row>
     <row r="14">
@@ -3068,39 +3068,63 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>PUERTAS DE SEGURIDAD</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>199.8</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>199.8</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>SAL SOLUBLE</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C15" s="2" t="n">
         <v>360</v>
       </c>
-      <c r="D14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2" t="n">
+      <c r="D15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2" t="n">
         <v>360</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="7" t="inlineStr">
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>45565.95</v>
-      </c>
-      <c r="D15" s="2" t="n">
+      <c r="C16" s="2" t="n">
+        <v>45680.95</v>
+      </c>
+      <c r="D16" s="2" t="n">
         <v>17462.46</v>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>28103.49</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>0.3832348497068534</v>
+      <c r="E16" s="2" t="n">
+        <v>28218.49</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0.3822700710033394</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>316.8</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
@@ -1188,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>261</v>
+        <v>1101.94</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0</v>
+        <v>782.1</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>0</v>
@@ -1320,7 +1320,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>0</v>
+        <v>4508.97</v>
       </c>
       <c r="N14" s="2" t="n">
         <v>0</v>
@@ -1946,52 +1946,52 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
+          <t>2 de 23</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
           <t>1 de 23</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>0 de 23</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>0 de 23</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>3 de 23</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>1 de 23</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>0 de 23</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>1 de 23</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>0 de 23</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>2 de 23</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>1 de 23</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>0 de 23</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>1 de 23</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>0 de 23</t>
-        </is>
-      </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>5 de 23</t>
+          <t>6 de 23</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2371,7 +2371,7 @@
         <v>5296.63</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>3280.68</v>
+        <v>4438.42</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>6000</v>
@@ -2425,7 +2425,7 @@
         <v>6009.13</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>438.21</v>
+        <v>5729.28</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>6500</v>
@@ -2712,7 +2712,7 @@
         <v>59467.53</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>17462.46</v>
+        <v>23911.27</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>
@@ -2736,7 +2736,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -2811,13 +2811,13 @@
         <v>2183</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1396.8</v>
+        <v>1713.6</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>786.2</v>
+        <v>469.4000000000001</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.6398534127347687</v>
+        <v>0.7849748053137883</v>
       </c>
     </row>
     <row r="4">
@@ -2883,13 +2883,13 @@
         <v>3450</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1848.6</v>
+        <v>2630.7</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1601.4</v>
+        <v>819.3000000000002</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.5358260869565217</v>
+        <v>0.7625217391304348</v>
       </c>
     </row>
     <row r="7">
@@ -2907,13 +2907,13 @@
         <v>347.55</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>261</v>
+        <v>1101.94</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>86.55000000000001</v>
+        <v>-754.3900000000001</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7509710832973673</v>
+        <v>3.170594159113797</v>
       </c>
     </row>
     <row r="8">
@@ -3051,13 +3051,13 @@
         <v>36687</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>11625.09</v>
+        <v>16134.06</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>25061.91</v>
+        <v>20552.94</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.3168721890587947</v>
+        <v>0.4397759424319241</v>
       </c>
     </row>
     <row r="14">
@@ -3118,13 +3118,13 @@
         <v>45680.95</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>17462.46</v>
+        <v>23911.27</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>28218.49</v>
+        <v>21769.68</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.3822700710033394</v>
+        <v>0.5234407340477814</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -2344,7 +2344,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2866.5</v>
+        <v>2844.2</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>1000</v>
@@ -2712,7 +2712,7 @@
         <v>59467.53</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>23911.27</v>
+        <v>23888.97</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>
@@ -3003,13 +3003,13 @@
         <v>115</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1815.78</v>
+        <v>1793.48</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-1700.78</v>
+        <v>-1678.48</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>15.78939130434783</v>
+        <v>15.59547826086957</v>
       </c>
     </row>
     <row r="12">
@@ -3118,13 +3118,13 @@
         <v>45680.95</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>23911.27</v>
+        <v>23888.97</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>21769.68</v>
+        <v>21791.98</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.5234407340477814</v>
+        <v>0.5229525655661714</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -780,7 +780,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0</v>
+        <v>1111.97</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>0</v>
@@ -1320,7 +1320,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4508.97</v>
+        <v>9008.18</v>
       </c>
       <c r="N14" s="2" t="n">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>611.02</v>
+        <v>5818.17</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>0</v>
+        <v>6802.16</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
@@ -1905,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0</v>
+        <v>2389</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>0</v>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>3 de 23</t>
+          <t>4 de 23</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>6 de 23</t>
+          <t>8 de 23</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2039,7 +2039,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2182,7 +2182,7 @@
         <v>84.59</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1396.8</v>
+        <v>2508.77</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>5000</v>
@@ -2425,7 +2425,7 @@
         <v>6009.13</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>5729.28</v>
+        <v>10228.49</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>6500</v>
@@ -2452,7 +2452,7 @@
         <v>2701.41</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>611.02</v>
+        <v>5818.17</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>6500</v>
@@ -2533,7 +2533,7 @@
         <v>675.3200000000001</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0</v>
+        <v>6802.16</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>5000</v>
@@ -2695,7 +2695,7 @@
         <v>19795.02</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0</v>
+        <v>2389</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>7000</v>
@@ -2712,7 +2712,7 @@
         <v>59467.53</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>23888.97</v>
+        <v>43898.46</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>
@@ -2883,13 +2883,13 @@
         <v>3450</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2630.7</v>
+        <v>5019.7</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>819.3000000000002</v>
+        <v>-1569.7</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.7625217391304348</v>
+        <v>1.454985507246377</v>
       </c>
     </row>
     <row r="7">
@@ -3051,13 +3051,13 @@
         <v>36687</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>16134.06</v>
+        <v>33754.55</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>20552.94</v>
+        <v>2932.449999999997</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.4397759424319241</v>
+        <v>0.9200684166053371</v>
       </c>
     </row>
     <row r="14">
@@ -3118,13 +3118,13 @@
         <v>45680.95</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>23888.97</v>
+        <v>43898.46000000001</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>21791.98</v>
+        <v>1782.489999999997</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.5229525655661714</v>
+        <v>0.9609795768257885</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1396.8</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
@@ -780,7 +780,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1111.97</v>
+        <v>0</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>0</v>
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-27</v>
+        <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1134,13 +1134,13 @@
         <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>45.68</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>759.72</v>
+        <v>0</v>
       </c>
       <c r="N11" s="2" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>316.8</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
@@ -1188,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1101.94</v>
+        <v>0</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3019.68</v>
+        <v>0</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -1296,7 +1296,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>438.21</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>782.1</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>0</v>
@@ -1320,7 +1320,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>9008.18</v>
+        <v>0</v>
       </c>
       <c r="N14" s="2" t="n">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>5818.17</v>
+        <v>0</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -1485,7 +1485,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>908.1</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2600.55</v>
+        <v>0</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>6802.16</v>
+        <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>4661.12</v>
+        <v>0</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>940.5</v>
+        <v>0</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>0</v>
@@ -1905,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>2389</v>
+        <v>0</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>0</v>
@@ -1946,12 +1946,12 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2 de 23</t>
+          <t>0 de 23</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>1 de 23</t>
+          <t>0 de 23</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1966,12 +1966,12 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>4 de 23</t>
+          <t>0 de 23</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>1 de 23</t>
+          <t>0 de 23</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>1 de 23</t>
+          <t>0 de 23</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>8 de 23</t>
+          <t>0 de 23</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2036,10 +2036,10 @@
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2056,22 +2056,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>diciembre</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>diciembre</t>
+          <t>enero</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>enero</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2173,16 +2173,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>9421.780000000001</v>
+        <v>3063.25</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>3063.25</v>
+        <v>84.59</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>84.59</v>
+        <v>5457.09</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2508.77</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>5000</v>
@@ -2203,10 +2203,10 @@
         <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>77.69</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>77.69</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -2227,16 +2227,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>7713.51</v>
+        <v>10679.6</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>10679.6</v>
+        <v>19194.12</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>19194.12</v>
+        <v>3543.89</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-27</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>5000</v>
@@ -2257,10 +2257,10 @@
         <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>202.51</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>202.51</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
@@ -2284,10 +2284,10 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>1484.26</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1484.26</v>
+        <v>3632.07</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>507.6</v>
+        <v>0</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0</v>
+        <v>2844.2</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2844.2</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>1000</v>
@@ -2362,16 +2362,16 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>5172.27</v>
+        <v>9948.6</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>9948.6</v>
+        <v>5296.63</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>5296.63</v>
+        <v>4438.42</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>4438.42</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>6000</v>
@@ -2416,16 +2416,16 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>-494.21</v>
+        <v>12825.62</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>12825.62</v>
+        <v>6009.13</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>6009.13</v>
+        <v>10228.49</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>10228.49</v>
+        <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>6500</v>
@@ -2443,16 +2443,16 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4850.15</v>
+        <v>9712.51</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>9712.51</v>
+        <v>2701.41</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2701.41</v>
+        <v>5818.17</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>5818.17</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>6500</v>
@@ -2497,16 +2497,16 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>3156.1</v>
+        <v>2698.29</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>2698.29</v>
+        <v>3091.73</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>3091.73</v>
+        <v>3539.95</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>3539.95</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>1500</v>
@@ -2524,16 +2524,16 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>16276.37</v>
+        <v>4419.18</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>4419.18</v>
+        <v>675.3200000000001</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>675.3200000000001</v>
+        <v>6802.16</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>6802.16</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>5000</v>
@@ -2608,13 +2608,13 @@
         <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0</v>
+        <v>-496.35</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-496.35</v>
+        <v>4415.8</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>4415.8</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0</v>
@@ -2662,13 +2662,13 @@
         <v>0</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0</v>
+        <v>1351.47</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1351.47</v>
+        <v>940.5</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>940.5</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -2686,16 +2686,16 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>4205.02</v>
+        <v>13320.25</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>13320.25</v>
+        <v>19795.02</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>19795.02</v>
+        <v>2389</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>2389</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>7000</v>
@@ -2703,16 +2703,16 @@
     </row>
     <row r="25">
       <c r="C25" s="6" t="n">
-        <v>50808.59</v>
+        <v>66667.3</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>66667.3</v>
+        <v>59467.53</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>59467.53</v>
+        <v>54049.74</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>43898.46</v>
+        <v>0</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -2735,9 +2735,9 @@
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2811,13 +2811,13 @@
         <v>2183</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1713.6</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>469.4000000000001</v>
+        <v>2183</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.7849748053137883</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2835,13 +2835,13 @@
         <v>584</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>438.21</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>145.79</v>
+        <v>584</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.7503595890410959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2880,16 +2880,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3450</v>
+        <v>2350</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>5019.7</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-1569.7</v>
+        <v>2350</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.454985507246377</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2907,13 +2907,13 @@
         <v>347.55</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1101.94</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-754.3900000000001</v>
+        <v>347.55</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.170594159113797</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2955,10 +2955,10 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>31.3</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-31.3</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -2979,13 +2979,13 @@
         <v>728.7</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>45.68</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>683.0200000000001</v>
+        <v>728.7</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.06268697680801427</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -3003,13 +3003,13 @@
         <v>115</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1793.48</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-1678.48</v>
+        <v>115</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>15.59547826086957</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3048,16 +3048,16 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>36687</v>
+        <v>32950</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>33754.55</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2932.449999999997</v>
+        <v>32950</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9200684166053371</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3115,16 +3115,16 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>45680.95</v>
+        <v>40843.95</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>43898.46000000001</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1782.489999999997</v>
+        <v>40843.95</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.9609795768257885</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>1222.04</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>0 de 23</t>
+          <t>1 de 23</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2290,7 +2290,7 @@
         <v>3632.07</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
+        <v>1222.04</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>5000</v>
@@ -2712,7 +2712,7 @@
         <v>54049.74</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0</v>
+        <v>1222.04</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>
@@ -2735,9 +2735,9 @@
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3051,13 +3051,13 @@
         <v>32950</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>1222.04</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>32950</v>
+        <v>31727.96</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>0.03708770864946889</v>
       </c>
     </row>
     <row r="14">
@@ -3118,13 +3118,13 @@
         <v>40843.95</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0</v>
+        <v>1222.04</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>40843.95</v>
+        <v>39621.91</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0</v>
+        <v>0.02991973107400239</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1845,7 +1845,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0</v>
+        <v>-658.35</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>0</v>
@@ -2668,7 +2668,7 @@
         <v>940.5</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0</v>
+        <v>-658.35</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -2712,7 +2712,7 @@
         <v>54049.74</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1222.04</v>
+        <v>563.6899999999999</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>
@@ -2883,13 +2883,13 @@
         <v>2350</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>-658.35</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2350</v>
+        <v>3008.35</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>-0.2801489361702128</v>
       </c>
     </row>
     <row r="7">
@@ -3118,13 +3118,13 @@
         <v>40843.95</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1222.04</v>
+        <v>563.6899999999999</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>39621.91</v>
+        <v>40280.26</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.02991973107400239</v>
+        <v>0.01380106478438055</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1845,7 +1845,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>-658.35</v>
+        <v>-1504.8</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>0</v>
@@ -2668,7 +2668,7 @@
         <v>940.5</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-658.35</v>
+        <v>-1504.8</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -2712,7 +2712,7 @@
         <v>54049.74</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>563.6899999999999</v>
+        <v>-282.76</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>
@@ -2883,13 +2883,13 @@
         <v>2350</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-658.35</v>
+        <v>-1504.8</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3008.35</v>
+        <v>3854.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.2801489361702128</v>
+        <v>-0.6403404255319148</v>
       </c>
     </row>
     <row r="7">
@@ -3118,13 +3118,13 @@
         <v>40843.95</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>563.6899999999999</v>
+        <v>-282.76</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>40280.26</v>
+        <v>41126.71000000001</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.01380106478438055</v>
+        <v>-0.00692293473084753</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1134,7 +1134,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>-45.68</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -2344,7 +2344,7 @@
         <v>2844.2</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0</v>
+        <v>-45.68</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>1000</v>
@@ -2712,7 +2712,7 @@
         <v>54049.74</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-282.76</v>
+        <v>-328.44</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>
@@ -2737,7 +2737,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2979,13 +2979,13 @@
         <v>728.7</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>-45.68</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>728.7</v>
+        <v>774.38</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>-0.06268697680801427</v>
       </c>
     </row>
     <row r="11">
@@ -3118,13 +3118,13 @@
         <v>40843.95</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>-282.76</v>
+        <v>-328.4400000000001</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>41126.71000000001</v>
+        <v>41172.39</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.00692293473084753</v>
+        <v>-0.008041337823594437</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>1115.22</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1485,7 +1485,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0</v>
+        <v>782.1</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0</v>
+        <v>1280.37</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1966,32 +1966,32 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
+          <t>1 de 23</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
           <t>0 de 23</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>0 de 23</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>0 de 23</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>0 de 23</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>0 de 23</t>
-        </is>
-      </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>1 de 23</t>
+          <t>3 de 23</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2236,7 +2236,7 @@
         <v>3543.89</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
+        <v>1115.22</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>5000</v>
@@ -2506,7 +2506,7 @@
         <v>3539.95</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0</v>
+        <v>2062.47</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>1500</v>
@@ -2712,7 +2712,7 @@
         <v>54049.74</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-328.44</v>
+        <v>2849.25</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>
@@ -2883,13 +2883,13 @@
         <v>2350</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-1504.8</v>
+        <v>-722.7</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3854.8</v>
+        <v>3072.7</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.6403404255319148</v>
+        <v>-0.307531914893617</v>
       </c>
     </row>
     <row r="7">
@@ -3051,13 +3051,13 @@
         <v>32950</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1222.04</v>
+        <v>3617.63</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>31727.96</v>
+        <v>29332.37</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.03708770864946889</v>
+        <v>0.109791502276176</v>
       </c>
     </row>
     <row r="14">
@@ -3118,13 +3118,13 @@
         <v>40843.95</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>-328.4400000000001</v>
+        <v>2849.25</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>41172.39</v>
+        <v>37994.7</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.008041337823594437</v>
+        <v>0.06975941357287921</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0</v>
+        <v>1128.6</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>0</v>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>1 de 23</t>
+          <t>2 de 23</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -2425,7 +2425,7 @@
         <v>10228.49</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0</v>
+        <v>1128.6</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>6500</v>
@@ -2712,7 +2712,7 @@
         <v>54049.74</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>2849.25</v>
+        <v>3977.85</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>
@@ -2883,13 +2883,13 @@
         <v>2350</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-722.7</v>
+        <v>405.9</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3072.7</v>
+        <v>1944.1</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.307531914893617</v>
+        <v>0.1727234042553192</v>
       </c>
     </row>
     <row r="7">
@@ -3118,13 +3118,13 @@
         <v>40843.95</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>2849.25</v>
+        <v>3977.85</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>37994.7</v>
+        <v>36866.10000000001</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.06975941357287921</v>
+        <v>0.09739141292651664</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -1389,7 +1389,7 @@
         <v>0</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q15" s="2" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>3 de 23</t>
+          <t>4 de 23</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>0 de 23</t>
+          <t>1 de 23</t>
         </is>
       </c>
       <c r="Q25" s="4" t="inlineStr">
@@ -2452,7 +2452,7 @@
         <v>5818.17</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>6500</v>
@@ -2712,7 +2712,7 @@
         <v>54049.74</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>3977.85</v>
+        <v>3986.22</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>
@@ -2931,13 +2931,13 @@
         <v>250</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>250</v>
+        <v>247.88</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>0.00848</v>
       </c>
     </row>
     <row r="9">
@@ -3051,13 +3051,13 @@
         <v>32950</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>3617.63</v>
+        <v>3623.88</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>29332.37</v>
+        <v>29326.12</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.109791502276176</v>
+        <v>0.1099811836115326</v>
       </c>
     </row>
     <row r="14">
@@ -3118,13 +3118,13 @@
         <v>40843.95</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>3977.85</v>
+        <v>3986.22</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>36866.10000000001</v>
+        <v>36857.73</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.09739141292651664</v>
+        <v>0.09759633923751253</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0</v>
+        <v>782.1</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>0</v>
+        <v>1111.97</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>2 de 23</t>
+          <t>3 de 23</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>4 de 23</t>
+          <t>6 de 23</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2371,7 +2371,7 @@
         <v>4438.42</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0</v>
+        <v>1894.07</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>6000</v>
@@ -2668,7 +2668,7 @@
         <v>940.5</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-1504.8</v>
+        <v>-1494</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -2712,7 +2712,7 @@
         <v>54049.74</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>3986.22</v>
+        <v>5891.089999999999</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>
@@ -2883,13 +2883,13 @@
         <v>2350</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>405.9</v>
+        <v>1188</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1944.1</v>
+        <v>1162</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1727234042553192</v>
+        <v>0.505531914893617</v>
       </c>
     </row>
     <row r="7">
@@ -3051,13 +3051,13 @@
         <v>32950</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>3623.88</v>
+        <v>4746.65</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>29326.12</v>
+        <v>28203.35</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.1099811836115326</v>
+        <v>0.1440561456752655</v>
       </c>
     </row>
     <row r="14">
@@ -3118,13 +3118,13 @@
         <v>40843.95</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>3986.22</v>
+        <v>5891.089999999999</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>36857.73</v>
+        <v>34952.86</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.09759633923751253</v>
+        <v>0.1442340909730817</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1222.04</v>
+        <v>1202.95</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -2290,7 +2290,7 @@
         <v>3632.07</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1222.04</v>
+        <v>1202.95</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>5000</v>
@@ -2712,7 +2712,7 @@
         <v>54049.74</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>5891.089999999999</v>
+        <v>5872</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>
@@ -3051,13 +3051,13 @@
         <v>32950</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>4746.65</v>
+        <v>4727.56</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>28203.35</v>
+        <v>28222.44</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.1440561456752655</v>
+        <v>0.1434767830045524</v>
       </c>
     </row>
     <row r="14">
@@ -3118,13 +3118,13 @@
         <v>40843.95</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>5891.089999999999</v>
+        <v>5872</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>34952.86</v>
+        <v>34971.95</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.1442340909730817</v>
+        <v>0.1437667022900576</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>6.25</v>
+        <v>2526.71</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>5818.17</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>8.369999999999999</v>
+        <v>2528.83</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>6500</v>
@@ -2712,7 +2712,7 @@
         <v>54049.74</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>5872</v>
+        <v>8392.459999999999</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>
@@ -3051,13 +3051,13 @@
         <v>32950</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>4727.56</v>
+        <v>7248.02</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>28222.44</v>
+        <v>25701.98</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.1434767830045524</v>
+        <v>0.2199702579666161</v>
       </c>
     </row>
     <row r="14">
@@ -3118,13 +3118,13 @@
         <v>40843.95</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>5872</v>
+        <v>8392.460000000001</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>34971.95</v>
+        <v>32451.49</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.1437667022900576</v>
+        <v>0.2054762088387631</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2526.71</v>
+        <v>1896.59</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>5818.17</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>2528.83</v>
+        <v>1898.71</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>6500</v>
@@ -2712,7 +2712,7 @@
         <v>54049.74</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>8392.459999999999</v>
+        <v>7762.34</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>
@@ -2735,7 +2735,7 @@
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3051,13 +3051,13 @@
         <v>32950</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>7248.02</v>
+        <v>6617.9</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>25701.98</v>
+        <v>26332.1</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.2199702579666161</v>
+        <v>0.2008467374810319</v>
       </c>
     </row>
     <row r="14">
@@ -3118,13 +3118,13 @@
         <v>40843.95</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>8392.460000000001</v>
+        <v>7762.339999999999</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>32451.49</v>
+        <v>33081.61</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.2054762088387631</v>
+        <v>0.1900487097844356</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1485,7 +1485,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>782.1</v>
+        <v>714.45</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>0</v>
@@ -2506,7 +2506,7 @@
         <v>3539.95</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>2062.47</v>
+        <v>1994.82</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>1500</v>
@@ -2712,7 +2712,7 @@
         <v>54049.74</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>7762.34</v>
+        <v>7694.69</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>
@@ -2735,7 +2735,7 @@
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
@@ -2883,13 +2883,13 @@
         <v>2350</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1188</v>
+        <v>1120.35</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1162</v>
+        <v>1229.65</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.505531914893617</v>
+        <v>0.4767446808510638</v>
       </c>
     </row>
     <row r="7">
@@ -3118,13 +3118,13 @@
         <v>40843.95</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7762.339999999999</v>
+        <v>7694.69</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>33081.61</v>
+        <v>33149.26</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.1900487097844356</v>
+        <v>0.1883924057296123</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1115.22</v>
+        <v>2875.17</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1353,7 +1353,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>457.92</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1896.59</v>
+        <v>6538.96</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>0 de 23</t>
+          <t>1 de 23</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -2236,7 +2236,7 @@
         <v>3543.89</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1115.22</v>
+        <v>2875.17</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>5000</v>
@@ -2452,7 +2452,7 @@
         <v>5818.17</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1898.71</v>
+        <v>6999</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>6500</v>
@@ -2712,7 +2712,7 @@
         <v>54049.74</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>7694.69</v>
+        <v>14554.93</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>
@@ -2735,7 +2735,7 @@
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
@@ -2811,13 +2811,13 @@
         <v>2183</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>457.92</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2183</v>
+        <v>1725.08</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>0.2097663765460376</v>
       </c>
     </row>
     <row r="4">
@@ -3051,13 +3051,13 @@
         <v>32950</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6617.9</v>
+        <v>13020.22</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>26332.1</v>
+        <v>19929.78</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.2008467374810319</v>
+        <v>0.3951508345978755</v>
       </c>
     </row>
     <row r="14">
@@ -3118,13 +3118,13 @@
         <v>40843.95</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7694.69</v>
+        <v>14554.93</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>33149.26</v>
+        <v>26289.02</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.1883924057296123</v>
+        <v>0.3563546131067146</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>6538.96</v>
+        <v>7310.71</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>5818.17</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>6999</v>
+        <v>7770.75</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>6500</v>
@@ -2712,7 +2712,7 @@
         <v>54049.74</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>14554.93</v>
+        <v>15326.68</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>
@@ -3051,13 +3051,13 @@
         <v>32950</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>13020.22</v>
+        <v>13791.97</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>19929.78</v>
+        <v>19158.03</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.3951508345978755</v>
+        <v>0.4185726858877086</v>
       </c>
     </row>
     <row r="14">
@@ -3118,13 +3118,13 @@
         <v>40843.95</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>14554.93</v>
+        <v>15326.68</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>26289.02</v>
+        <v>25517.27</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.3563546131067146</v>
+        <v>0.3752497003840225</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2875.17</v>
+        <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1202.95</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -1134,7 +1134,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-45.68</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>782.1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1111.97</v>
+        <v>0</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1128.6</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>0</v>
@@ -1353,7 +1353,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>457.92</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>7310.71</v>
+        <v>0</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -1389,7 +1389,7 @@
         <v>0</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="2" t="n">
         <v>0</v>
@@ -1485,7 +1485,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>714.45</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1280.37</v>
+        <v>0</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>-1504.8</v>
+        <v>0</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1 de 23</t>
+          <t>0 de 23</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>3 de 23</t>
+          <t>0 de 23</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>6 de 23</t>
+          <t>0 de 23</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>1 de 23</t>
+          <t>0 de 23</t>
         </is>
       </c>
       <c r="Q25" s="4" t="inlineStr">
@@ -2037,9 +2037,9 @@
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="47" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2056,22 +2056,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>diciembre</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>diciembre</t>
+          <t>enero</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>enero</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2173,13 +2173,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3063.25</v>
+        <v>84.59</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>84.59</v>
+        <v>5457.09</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>5457.09</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>77.69</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>77.69</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
@@ -2227,16 +2227,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>10679.6</v>
+        <v>19194.12</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>19194.12</v>
+        <v>3543.89</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>3543.89</v>
+        <v>2875.17</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2875.17</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>5000</v>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0</v>
+        <v>202.51</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>202.51</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>0</v>
@@ -2281,16 +2281,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0</v>
+        <v>1484.26</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1484.26</v>
+        <v>3632.07</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3632.07</v>
+        <v>1202.95</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1202.95</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>5000</v>
@@ -2338,13 +2338,13 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>2844.2</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2844.2</v>
+        <v>-45.68</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-45.68</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>1000</v>
@@ -2362,16 +2362,16 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>9948.6</v>
+        <v>5296.63</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>5296.63</v>
+        <v>4438.42</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>4438.42</v>
+        <v>1894.07</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1894.07</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>6000</v>
@@ -2416,16 +2416,16 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>12825.62</v>
+        <v>6009.13</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6009.13</v>
+        <v>10228.49</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>10228.49</v>
+        <v>1128.6</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1128.6</v>
+        <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>6500</v>
@@ -2443,16 +2443,16 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>9712.51</v>
+        <v>2701.41</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>2701.41</v>
+        <v>5818.17</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>5818.17</v>
+        <v>7770.75</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>7770.75</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>6500</v>
@@ -2497,16 +2497,16 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>2698.29</v>
+        <v>3091.73</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>3091.73</v>
+        <v>3539.95</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>3539.95</v>
+        <v>1994.82</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1994.82</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>1500</v>
@@ -2524,13 +2524,13 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>4419.18</v>
+        <v>675.3200000000001</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>675.3200000000001</v>
+        <v>6802.16</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>6802.16</v>
+        <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
@@ -2605,13 +2605,13 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0</v>
+        <v>-496.35</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>-496.35</v>
+        <v>4415.8</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>4415.8</v>
+        <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>0</v>
@@ -2659,16 +2659,16 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0</v>
+        <v>1351.47</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1351.47</v>
+        <v>940.5</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>940.5</v>
+        <v>-1494</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-1494</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>13320.25</v>
+        <v>19795.02</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>19795.02</v>
+        <v>2389</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>2389</v>
+        <v>0</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
@@ -2703,16 +2703,16 @@
     </row>
     <row r="25">
       <c r="C25" s="6" t="n">
-        <v>66667.3</v>
+        <v>59467.53</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>59467.53</v>
+        <v>54049.74</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>54049.74</v>
+        <v>15326.68</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>15326.68</v>
+        <v>0</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -2031,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -2040,7 +2040,6 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2074,11 +2073,6 @@
           <t>marzo</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>PRESUPUESTO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2103,9 +2097,6 @@
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2130,9 +2121,6 @@
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2157,9 +2145,6 @@
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2184,9 +2169,6 @@
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="2" t="n">
-        <v>5000</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2211,9 +2193,6 @@
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2238,9 +2217,6 @@
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="2" t="n">
-        <v>5000</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2265,9 +2241,6 @@
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="2" t="n">
-        <v>500</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2292,9 +2265,6 @@
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="2" t="n">
-        <v>5000</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2319,9 +2289,6 @@
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2346,9 +2313,6 @@
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="2" t="n">
-        <v>1000</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2373,9 +2337,6 @@
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="2" t="n">
-        <v>6000</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2400,9 +2361,6 @@
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2427,9 +2385,6 @@
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="2" t="n">
-        <v>6500</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2454,9 +2409,6 @@
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="2" t="n">
-        <v>6500</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2481,9 +2433,6 @@
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2508,9 +2457,6 @@
       <c r="F17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="2" t="n">
-        <v>1500</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2535,9 +2481,6 @@
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="2" t="n">
-        <v>5000</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2562,9 +2505,6 @@
       <c r="F19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2589,9 +2529,6 @@
       <c r="F20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2616,9 +2553,6 @@
       <c r="F21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2643,9 +2577,6 @@
       <c r="F22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2670,9 +2601,6 @@
       <c r="F23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2696,9 +2624,6 @@
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>7000</v>
       </c>
     </row>
     <row r="25">
@@ -2713,9 +2638,6 @@
       </c>
       <c r="F25" s="6" t="n">
         <v>0</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>49000</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -2031,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2040,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2073,6 +2074,11 @@
           <t>marzo</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>PRESUPUESTO</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2097,6 +2103,9 @@
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G2" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2121,6 +2130,9 @@
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G3" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2145,6 +2157,9 @@
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G4" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2169,6 +2184,9 @@
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G5" s="2" t="n">
+        <v>5000</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2193,6 +2211,9 @@
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G6" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2217,6 +2238,9 @@
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G7" s="2" t="n">
+        <v>5000</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2241,6 +2265,9 @@
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G8" s="2" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2265,6 +2292,9 @@
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G9" s="2" t="n">
+        <v>5000</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2289,6 +2319,9 @@
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G10" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2313,6 +2346,9 @@
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G11" s="2" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2337,6 +2373,9 @@
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G12" s="2" t="n">
+        <v>6000</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2361,6 +2400,9 @@
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G13" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2385,6 +2427,9 @@
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G14" s="2" t="n">
+        <v>6500</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2409,6 +2454,9 @@
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G15" s="2" t="n">
+        <v>6500</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2433,6 +2481,9 @@
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G16" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2457,6 +2508,9 @@
       <c r="F17" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G17" s="2" t="n">
+        <v>1500</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2481,6 +2535,9 @@
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G18" s="2" t="n">
+        <v>5000</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2505,6 +2562,9 @@
       <c r="F19" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G19" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2529,6 +2589,9 @@
       <c r="F20" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G20" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2553,6 +2616,9 @@
       <c r="F21" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G21" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2577,6 +2643,9 @@
       <c r="F22" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G22" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2601,6 +2670,9 @@
       <c r="F23" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G23" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2624,6 +2696,9 @@
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>7000</v>
       </c>
     </row>
     <row r="25">
@@ -2638,6 +2713,9 @@
       </c>
       <c r="F25" s="6" t="n">
         <v>0</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>49000</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -2729,15 +2729,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2811,13 +2811,13 @@
         <v>2183</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>457.92</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1725.08</v>
+        <v>2183</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.2097663765460376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2832,13 +2832,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>584</v>
+        <v>199.5</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>584</v>
+        <v>199.5</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
@@ -2880,16 +2880,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2350</v>
+        <v>240</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1120.35</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1229.65</v>
+        <v>240</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.4767446808510638</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2904,13 +2904,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>347.55</v>
+        <v>263</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>347.55</v>
+        <v>263</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -2931,13 +2931,13 @@
         <v>250</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>247.88</v>
+        <v>250</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.00848</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2976,16 +2976,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>728.7</v>
+        <v>407</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>-45.68</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>774.38</v>
+        <v>407</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-0.06268697680801427</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -3048,16 +3048,16 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>32950</v>
+        <v>52623</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>13791.97</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>19158.03</v>
+        <v>52623</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.4185726858877086</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3085,46 +3085,22 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>SAL SOLUBLE</t>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>360</v>
+        <v>57256.2</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>360</v>
+        <v>57256.2</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>40843.95</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>15326.68</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>25517.27</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>0.3752497003840225</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>0</v>
+        <v>1176.46</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>0 de 23</t>
+          <t>1 de 23</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2039,7 +2039,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2371,7 +2371,7 @@
         <v>1894.07</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0</v>
+        <v>1176.46</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>6000</v>
@@ -2712,7 +2712,7 @@
         <v>15326.68</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0</v>
+        <v>1176.46</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>
@@ -2735,9 +2735,9 @@
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3051,13 +3051,13 @@
         <v>52623</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>1176.46</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>52623</v>
+        <v>51446.54</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>0.02235638409060677</v>
       </c>
     </row>
     <row r="14">
@@ -3094,13 +3094,13 @@
         <v>57256.2</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>1176.46</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>57256.2</v>
+        <v>56079.74000000001</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0</v>
+        <v>0.02054729444147533</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>1591.57</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1353,7 +1353,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>2719.84</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>0</v>
@@ -1377,10 +1377,10 @@
         <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>2869.45</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0</v>
+        <v>2315.25</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -1946,52 +1946,52 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
+          <t>1 de 23</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
           <t>0 de 23</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>0 de 23</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>0 de 23</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>0 de 23</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>0 de 23</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>0 de 23</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>0 de 23</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>0 de 23</t>
-        </is>
-      </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>0 de 23</t>
+          <t>1 de 23</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>1 de 23</t>
+          <t>3 de 23</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2236,7 +2236,7 @@
         <v>2875.17</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
+        <v>1591.57</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>5000</v>
@@ -2452,7 +2452,7 @@
         <v>7770.75</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>7904.54</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>6500</v>
@@ -2712,7 +2712,7 @@
         <v>15326.68</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1176.46</v>
+        <v>10672.57</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>49000</v>
@@ -2736,7 +2736,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -2811,13 +2811,13 @@
         <v>2183</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>2719.84</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2183</v>
+        <v>-536.8400000000001</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>1.245918460833715</v>
       </c>
     </row>
     <row r="4">
@@ -3027,13 +3027,13 @@
         <v>467</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>2869.45</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>467</v>
+        <v>-2402.45</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>6.144432548179871</v>
       </c>
     </row>
     <row r="13">
@@ -3051,13 +3051,13 @@
         <v>52623</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1176.46</v>
+        <v>5083.28</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>51446.54</v>
+        <v>47539.72</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.02235638409060677</v>
+        <v>0.09659806548467399</v>
       </c>
     </row>
     <row r="14">
@@ -3094,13 +3094,13 @@
         <v>57256.2</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1176.46</v>
+        <v>10672.57</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>56079.74000000001</v>
+        <v>46583.63</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.02054729444147533</v>
+        <v>0.1864002501039189</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MATERIALES DE CONSTRUCCION SUPERMACONSVI S.A.</t>
+          <t>MARIN DELGADO BRENDA MARIA</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MEGAMAFERS S.A.</t>
+          <t>MATERIALES DE CONSTRUCCION SUPERMACONSVI S.A.</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -1346,14 +1346,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MUÑOZ LOZA ROMMEL SEBASTIAN</t>
+          <t>MEGAMAFERS S.A.</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>2719.84</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>0</v>
@@ -1377,10 +1377,10 @@
         <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>2869.45</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2315.25</v>
+        <v>0</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -1406,14 +1406,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ORTEGA PAREDES RUDHT ELENA</t>
+          <t>MUÑOZ LOZA ROMMEL SEBASTIAN</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0</v>
+        <v>2719.84</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>2869.45</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>0</v>
+        <v>2315.25</v>
       </c>
       <c r="N16" s="2" t="n">
         <v>0</v>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>OÑATE PEREZ MERCY YOLANDA</t>
+          <t>ORTEGA PAREDES RUDHT ELENA</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PADILLA MIER BERTHA MARIETA</t>
+          <t>OÑATE PEREZ MERCY YOLANDA</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PAVIMARSA S.A.</t>
+          <t>PADILLA MIER BERTHA MARIETA</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>REA ARMAS CARLOS FERNANDO</t>
+          <t>PAVIMARSA S.A.</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SARZOSA UNDA JOSE DOMINGO</t>
+          <t>REA ARMAS CARLOS FERNANDO</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SIGCHOS MORA FRANKLIN PORFIRIO</t>
+          <t>SARZOSA UNDA JOSE DOMINGO</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TRUJILLO TORRES VINICIO RUBEN</t>
+          <t>SIGCHOS MORA FRANKLIN PORFIRIO</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -1886,137 +1886,197 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>TRUJILLO TORRES VINICIO RUBEN</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>TULCAN NARVAEZ EDITH MARITZA</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>0 de 23</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>1 de 23</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>0 de 23</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>0 de 23</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>0 de 23</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>0 de 23</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>0 de 23</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>0 de 23</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>0 de 23</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>1 de 23</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>3 de 23</t>
-        </is>
-      </c>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t>0 de 23</t>
-        </is>
-      </c>
-      <c r="O25" s="4" t="inlineStr">
-        <is>
-          <t>0 de 23</t>
-        </is>
-      </c>
-      <c r="P25" s="4" t="inlineStr">
-        <is>
-          <t>0 de 23</t>
-        </is>
-      </c>
-      <c r="Q25" s="4" t="inlineStr">
-        <is>
-          <t>0 de 23</t>
-        </is>
-      </c>
-      <c r="R25" s="4" t="inlineStr">
-        <is>
-          <t>0 de 23</t>
+      <c r="C25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>1 de 24</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>1 de 24</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>3 de 24</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
+        </is>
+      </c>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
+        </is>
+      </c>
+      <c r="P26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
+        </is>
+      </c>
+      <c r="R26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -2385,7 +2445,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MATERIALES DE CONSTRUCCION SUPERMACONSVI S.A.</t>
+          <t>MARIN DELGADO BRENDA MARIA</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -2412,23 +2472,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MEGAMAFERS S.A.</t>
+          <t>MATERIALES DE CONSTRUCCION SUPERMACONSVI S.A.</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>6009.13</v>
+        <v>0</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>10228.49</v>
+        <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1128.6</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>6500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2439,20 +2499,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MUÑOZ LOZA ROMMEL SEBASTIAN</t>
+          <t>MEGAMAFERS S.A.</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>2701.41</v>
+        <v>6009.13</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>5818.17</v>
+        <v>10228.49</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>7770.75</v>
+        <v>1128.6</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>7904.54</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>6500</v>
@@ -2466,23 +2526,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ORTEGA PAREDES RUDHT ELENA</t>
+          <t>MUÑOZ LOZA ROMMEL SEBASTIAN</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0</v>
+        <v>2701.41</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0</v>
+        <v>5818.17</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0</v>
+        <v>7770.75</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0</v>
+        <v>7904.54</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="17">
@@ -2493,23 +2553,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>OÑATE PEREZ MERCY YOLANDA</t>
+          <t>ORTEGA PAREDES RUDHT ELENA</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>3091.73</v>
+        <v>0</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>3539.95</v>
+        <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1994.82</v>
+        <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2520,23 +2580,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PADILLA MIER BERTHA MARIETA</t>
+          <t>OÑATE PEREZ MERCY YOLANDA</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>675.3200000000001</v>
+        <v>3091.73</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>6802.16</v>
+        <v>3539.95</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0</v>
+        <v>1994.82</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>5000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="19">
@@ -2547,14 +2607,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PAVIMARSA S.A.</t>
+          <t>PADILLA MIER BERTHA MARIETA</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0</v>
+        <v>675.3200000000001</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>6802.16</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
@@ -2563,7 +2623,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="20">
@@ -2574,7 +2634,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>REA ARMAS CARLOS FERNANDO</t>
+          <t>PAVIMARSA S.A.</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -2601,14 +2661,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SARZOSA UNDA JOSE DOMINGO</t>
+          <t>REA ARMAS CARLOS FERNANDO</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-496.35</v>
+        <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>4415.8</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0</v>
@@ -2628,14 +2688,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SIGCHOS MORA FRANKLIN PORFIRIO</t>
+          <t>SARZOSA UNDA JOSE DOMINGO</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0</v>
+        <v>-496.35</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>4415.8</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0</v>
@@ -2655,17 +2715,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TRUJILLO TORRES VINICIO RUBEN</t>
+          <t>SIGCHOS MORA FRANKLIN PORFIRIO</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>1351.47</v>
+        <v>0</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>940.5</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-1494</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>0</v>
@@ -2682,39 +2742,66 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>TRUJILLO TORRES VINICIO RUBEN</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>1351.47</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>940.5</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>-1494</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>TULCAN NARVAEZ EDITH MARITZA</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="C25" s="2" t="n">
         <v>19795.02</v>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D25" s="2" t="n">
         <v>2389</v>
       </c>
-      <c r="E24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="2" t="n">
+      <c r="E25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2" t="n">
         <v>7000</v>
       </c>
     </row>
-    <row r="25">
-      <c r="C25" s="6" t="n">
+    <row r="26">
+      <c r="C26" s="6" t="n">
         <v>59467.53</v>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D26" s="6" t="n">
         <v>54049.74</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="E26" s="6" t="n">
         <v>15326.68</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="F26" s="6" t="n">
         <v>10672.57</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="G26" s="6" t="n">
         <v>49000</v>
       </c>
     </row>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>0</v>
+        <v>150.8</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0</v>
+        <v>-67.69</v>
       </c>
       <c r="I25" s="2" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>3 de 24</t>
+          <t>4 de 24</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2458,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0</v>
+        <v>150.8</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0</v>
+        <v>-67.69</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>7000</v>
@@ -2799,7 +2799,7 @@
         <v>15326.68</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>10672.57</v>
+        <v>10755.68</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>49000</v>
@@ -2970,13 +2970,13 @@
         <v>240</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>-67.69</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>240</v>
+        <v>307.69</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>-0.2820416666666666</v>
       </c>
     </row>
     <row r="7">
@@ -3138,13 +3138,13 @@
         <v>52623</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>5083.28</v>
+        <v>5234.08</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>47539.72</v>
+        <v>47388.92</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.09659806548467399</v>
+        <v>0.09946373258841192</v>
       </c>
     </row>
     <row r="14">
@@ -3181,13 +3181,13 @@
         <v>57256.2</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>10672.57</v>
+        <v>10755.68</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>46583.63</v>
+        <v>46500.52</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.1864002501039189</v>
+        <v>0.187851795962708</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>-67.69</v>
+        <v>-321.11</v>
       </c>
       <c r="I25" s="2" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-67.69</v>
+        <v>-321.11</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>7000</v>
@@ -2799,7 +2799,7 @@
         <v>15326.68</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>10755.68</v>
+        <v>10502.26</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>49000</v>
@@ -2970,13 +2970,13 @@
         <v>240</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-67.69</v>
+        <v>-321.11</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>307.69</v>
+        <v>561.11</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.2820416666666666</v>
+        <v>-1.337958333333333</v>
       </c>
     </row>
     <row r="7">
@@ -3181,13 +3181,13 @@
         <v>57256.2</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>10755.68</v>
+        <v>10502.26</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>46500.52</v>
+        <v>46753.94</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.187851795962708</v>
+        <v>0.1834257250743151</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1236,7 +1236,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>150.8</v>
+        <v>472.57</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>0 de 24</t>
+          <t>1 de 24</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -2458,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>150.8</v>
+        <v>546.86</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
         <v>15326.68</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>10502.26</v>
+        <v>10898.32</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>49000</v>
@@ -2824,7 +2824,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2922,13 +2922,13 @@
         <v>199.5</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>199.5</v>
+        <v>125.21</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>0.3723809523809524</v>
       </c>
     </row>
     <row r="5">
@@ -3138,13 +3138,13 @@
         <v>52623</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>5234.08</v>
+        <v>5555.85</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>47388.92</v>
+        <v>47067.15</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.09946373258841192</v>
+        <v>0.1055783592725614</v>
       </c>
     </row>
     <row r="14">
@@ -3181,13 +3181,13 @@
         <v>57256.2</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>10502.26</v>
+        <v>10898.32</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>46753.94</v>
+        <v>46357.88</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.1834257250743151</v>
+        <v>0.1903430545512975</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>0</v>
+        <v>10141.34</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>4 de 24</t>
+          <t>5 de 24</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2782,7 +2782,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-321.11</v>
+        <v>9820.23</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>7000</v>
@@ -2799,7 +2799,7 @@
         <v>15326.68</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>10898.32</v>
+        <v>21039.66</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>49000</v>
@@ -2822,7 +2822,7 @@
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3138,13 +3138,13 @@
         <v>52623</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>5555.85</v>
+        <v>15697.19</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>47067.15</v>
+        <v>36925.81</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.1055783592725614</v>
+        <v>0.298295232122836</v>
       </c>
     </row>
     <row r="14">
@@ -3181,13 +3181,13 @@
         <v>57256.2</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>10898.32</v>
+        <v>21039.66</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>46357.88</v>
+        <v>36216.54</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.1903430545512975</v>
+        <v>0.3674651828098965</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>10141.34</v>
+        <v>20232.82</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
@@ -2099,7 +2099,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2782,7 +2782,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>9820.23</v>
+        <v>19911.71</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>7000</v>
@@ -2799,7 +2799,7 @@
         <v>15326.68</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>21039.66</v>
+        <v>31131.14</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>49000</v>
@@ -3138,13 +3138,13 @@
         <v>52623</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>15697.19</v>
+        <v>25788.67</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>36925.81</v>
+        <v>26834.33</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.298295232122836</v>
+        <v>0.4900646105315166</v>
       </c>
     </row>
     <row r="14">
@@ -3181,13 +3181,13 @@
         <v>57256.2</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>21039.66</v>
+        <v>31131.14</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>36216.54</v>
+        <v>26125.06</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.3674651828098965</v>
+        <v>0.5437164883453669</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>6156.27</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>2869.45</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2315.25</v>
+        <v>6095.94</v>
       </c>
       <c r="N16" s="2" t="n">
         <v>0</v>
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>0</v>
+        <v>11902.1</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>5 de 24</t>
+          <t>7 de 24</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2350,7 +2350,7 @@
         <v>1202.95</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
+        <v>6156.27</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>5000</v>
@@ -2404,7 +2404,7 @@
         <v>-45.68</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0</v>
+        <v>388.44</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>1000</v>
@@ -2539,7 +2539,7 @@
         <v>7770.75</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>7904.54</v>
+        <v>11685.23</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>6500</v>
@@ -2620,7 +2620,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0</v>
+        <v>11902.1</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>5000</v>
@@ -2799,7 +2799,7 @@
         <v>15326.68</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>31131.14</v>
+        <v>53358.64</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>49000</v>
@@ -3090,13 +3090,13 @@
         <v>115</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>388.44</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>115</v>
+        <v>-273.44</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>3.377739130434783</v>
       </c>
     </row>
     <row r="12">
@@ -3138,13 +3138,13 @@
         <v>52623</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>25788.67</v>
+        <v>47627.73</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>26834.33</v>
+        <v>4995.269999999997</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.4900646105315166</v>
+        <v>0.9050743971267318</v>
       </c>
     </row>
     <row r="14">
@@ -3181,13 +3181,13 @@
         <v>57256.2</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>31131.14</v>
+        <v>53358.64</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>26125.06</v>
+        <v>3897.559999999997</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.5437164883453669</v>
+        <v>0.9319277213646731</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1920,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>0</v>
+        <v>5686.6</v>
       </c>
       <c r="N24" s="2" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>7 de 24</t>
+          <t>8 de 24</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2755,7 +2755,7 @@
         <v>-1494</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0</v>
+        <v>5686.6</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
         <v>15326.68</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>53358.64</v>
+        <v>59045.24</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>49000</v>
@@ -3138,13 +3138,13 @@
         <v>52623</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>47627.73</v>
+        <v>53314.33</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>4995.269999999997</v>
+        <v>-691.3300000000017</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9050743971267318</v>
+        <v>1.013137411398058</v>
       </c>
     </row>
     <row r="14">
@@ -3181,13 +3181,13 @@
         <v>57256.2</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>53358.64</v>
+        <v>59045.24000000001</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>3897.559999999997</v>
+        <v>-1789.040000000002</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.9319277213646731</v>
+        <v>1.031246223116449</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -777,10 +777,10 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>1267.08</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0</v>
+        <v>5716.45</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>1267.08</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>1591.57</v>
@@ -1188,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>432.29</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1176.46</v>
+        <v>5077.01</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>11902.1</v>
+        <v>16038.62</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0</v>
@@ -1920,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>5686.6</v>
+        <v>6999.46</v>
       </c>
       <c r="N24" s="2" t="n">
         <v>0</v>
@@ -2031,27 +2031,27 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
+          <t>1 de 24</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
           <t>0 de 24</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>0 de 24</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>1 de 24</t>
+          <t>3 de 24</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>8 de 24</t>
+          <t>9 de 24</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2242,7 +2242,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0</v>
+        <v>6983.53</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>5000</v>
@@ -2296,7 +2296,7 @@
         <v>2875.17</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1591.57</v>
+        <v>2858.65</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>5000</v>
@@ -2431,7 +2431,7 @@
         <v>1894.07</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1176.46</v>
+        <v>5509.3</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>6000</v>
@@ -2620,7 +2620,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>11902.1</v>
+        <v>16038.62</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>5000</v>
@@ -2755,7 +2755,7 @@
         <v>-1494</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>5686.6</v>
+        <v>6999.46</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
         <v>15326.68</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>59045.24</v>
+        <v>77078.07000000001</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>49000</v>
@@ -2994,13 +2994,13 @@
         <v>263</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>432.29</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>263</v>
+        <v>-169.29</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>1.643688212927757</v>
       </c>
     </row>
     <row r="8">
@@ -3114,13 +3114,13 @@
         <v>467</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2869.45</v>
+        <v>5403.61</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-2402.45</v>
+        <v>-4936.61</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>6.144432548179871</v>
+        <v>11.57089935760171</v>
       </c>
     </row>
     <row r="13">
@@ -3138,13 +3138,13 @@
         <v>52623</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>53314.33</v>
+        <v>68380.71000000001</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-691.3300000000017</v>
+        <v>-15757.71000000001</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.013137411398058</v>
+        <v>1.299445299583832</v>
       </c>
     </row>
     <row r="14">
@@ -3181,13 +3181,13 @@
         <v>57256.2</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>59045.24000000001</v>
+        <v>77078.07000000001</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-1789.040000000002</v>
+        <v>-19821.87000000001</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1.031246223116449</v>
+        <v>1.346196045144456</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1920,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>6999.46</v>
+        <v>8054.4</v>
       </c>
       <c r="N24" s="2" t="n">
         <v>0</v>
@@ -2755,7 +2755,7 @@
         <v>-1494</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>6999.46</v>
+        <v>8054.4</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
         <v>15326.68</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>77078.07000000001</v>
+        <v>78133.00999999999</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>49000</v>
@@ -3138,13 +3138,13 @@
         <v>52623</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>68380.71000000001</v>
+        <v>69435.64999999999</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-15757.71000000001</v>
+        <v>-16812.64999999999</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.299445299583832</v>
+        <v>1.319492427265644</v>
       </c>
     </row>
     <row r="14">
@@ -3181,13 +3181,13 @@
         <v>57256.2</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>77078.07000000001</v>
+        <v>78133.00999999999</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-19821.87000000001</v>
+        <v>-20876.80999999999</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1.346196045144456</v>
+        <v>1.36462094934697</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>5077.01</v>
+        <v>3024.92</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -2431,7 +2431,7 @@
         <v>1894.07</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>5509.3</v>
+        <v>3457.21</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>6000</v>
@@ -2799,7 +2799,7 @@
         <v>15326.68</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>78133.00999999999</v>
+        <v>76080.92</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>49000</v>
@@ -3138,13 +3138,13 @@
         <v>52623</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>69435.64999999999</v>
+        <v>67383.56</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-16812.64999999999</v>
+        <v>-14760.56</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.319492427265644</v>
+        <v>1.280496360906828</v>
       </c>
     </row>
     <row r="14">
@@ -3181,13 +3181,13 @@
         <v>57256.2</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>78133.00999999999</v>
+        <v>76080.92</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-20876.80999999999</v>
+        <v>-18824.72</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1.36462094934697</v>
+        <v>1.328780463949756</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1140,7 +1140,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>0</v>
+        <v>1380.82</v>
       </c>
       <c r="N11" s="2" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>2869.45</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>6095.94</v>
+        <v>10381.09</v>
       </c>
       <c r="N16" s="2" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>9 de 24</t>
+          <t>10 de 24</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2404,7 +2404,7 @@
         <v>-45.68</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>388.44</v>
+        <v>1769.26</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>1000</v>
@@ -2539,7 +2539,7 @@
         <v>7770.75</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>11685.23</v>
+        <v>15970.38</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>6500</v>
@@ -2799,7 +2799,7 @@
         <v>15326.68</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>76080.92</v>
+        <v>81746.89</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>49000</v>
@@ -3138,13 +3138,13 @@
         <v>52623</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>67383.56</v>
+        <v>73049.53</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-14760.56</v>
+        <v>-20426.53</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.280496360906828</v>
+        <v>1.388167341276628</v>
       </c>
     </row>
     <row r="14">
@@ -3181,13 +3181,13 @@
         <v>57256.2</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>76080.92</v>
+        <v>81746.89</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-18824.72</v>
+        <v>-24490.69</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1.328780463949756</v>
+        <v>1.427738655377059</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -777,10 +777,10 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1267.08</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5716.45</v>
+        <v>0</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>0</v>
@@ -897,10 +897,10 @@
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>1267.08</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1591.57</v>
+        <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6156.27</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -1140,7 +1140,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1380.82</v>
+        <v>0</v>
       </c>
       <c r="N11" s="2" t="n">
         <v>0</v>
@@ -1188,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>432.29</v>
+        <v>0</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3024.92</v>
+        <v>0</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -1236,7 +1236,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>74.29000000000001</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>472.57</v>
+        <v>0</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>2719.84</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>2869.45</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>10381.09</v>
+        <v>0</v>
       </c>
       <c r="N16" s="2" t="n">
         <v>0</v>
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>16038.62</v>
+        <v>0</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0</v>
@@ -1920,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>8054.4</v>
+        <v>0</v>
       </c>
       <c r="N24" s="2" t="n">
         <v>0</v>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>-321.11</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2" t="n">
         <v>0</v>
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>20232.82</v>
+        <v>0</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>1 de 24</t>
+          <t>0 de 24</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>1 de 24</t>
+          <t>0 de 24</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>1 de 24</t>
+          <t>0 de 24</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>3 de 24</t>
+          <t>0 de 24</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>10 de 24</t>
+          <t>0 de 24</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2096,10 +2096,10 @@
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2116,22 +2116,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>diciembre</t>
+          <t>enero</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>enero</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2233,16 +2233,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>84.59</v>
+        <v>5457.09</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>5457.09</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>6983.53</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>6983.53</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>5000</v>
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>77.69</v>
+        <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
@@ -2287,16 +2287,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>19194.12</v>
+        <v>3543.89</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>3543.89</v>
+        <v>2875.17</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2875.17</v>
+        <v>5824.86</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2858.65</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>5000</v>
@@ -2314,7 +2314,7 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>202.51</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0</v>
@@ -2341,16 +2341,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1484.26</v>
+        <v>3632.07</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>3632.07</v>
+        <v>1202.95</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1202.95</v>
+        <v>6156.27</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>6156.27</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>5000</v>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0</v>
+        <v>2844.2</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2844.2</v>
+        <v>-45.68</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-45.68</v>
+        <v>1769.26</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1769.26</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>1000</v>
@@ -2422,16 +2422,16 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>5296.63</v>
+        <v>4438.42</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4438.42</v>
+        <v>1894.07</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1894.07</v>
+        <v>3457.21</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>3457.21</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>6000</v>
@@ -2455,10 +2455,10 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>546.86</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>546.86</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0</v>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>6009.13</v>
+        <v>10228.49</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>10228.49</v>
+        <v>1128.6</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1128.6</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
@@ -2530,16 +2530,16 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>2701.41</v>
+        <v>5818.17</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>5818.17</v>
+        <v>7770.75</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>7770.75</v>
+        <v>15970.38</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>15970.38</v>
+        <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>6500</v>
@@ -2584,13 +2584,13 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>3091.73</v>
+        <v>3539.95</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>3539.95</v>
+        <v>1994.82</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1994.82</v>
+        <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
@@ -2611,16 +2611,16 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>675.3200000000001</v>
+        <v>6802.16</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>6802.16</v>
+        <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0</v>
+        <v>16038.62</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>16038.62</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>5000</v>
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-496.35</v>
+        <v>4415.8</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>4415.8</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0</v>
@@ -2746,16 +2746,16 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>1351.47</v>
+        <v>940.5</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>940.5</v>
+        <v>-1494</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-1494</v>
+        <v>8054.4</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>8054.4</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0</v>
@@ -2773,16 +2773,16 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>19795.02</v>
+        <v>2389</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>2389</v>
+        <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0</v>
+        <v>21023.68</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>19911.71</v>
+        <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>7000</v>
@@ -2790,16 +2790,16 @@
     </row>
     <row r="26">
       <c r="C26" s="6" t="n">
-        <v>59467.53</v>
+        <v>54049.74</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>54049.74</v>
+        <v>15326.68</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>15326.68</v>
+        <v>85825.07000000001</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>81746.89</v>
+        <v>0</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>49000</v>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -2822,9 +2822,9 @@
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2871,13 +2871,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>136.08</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>136.08</v>
+        <v>0</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>0</v>
@@ -2895,16 +2895,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2183</v>
+        <v>2319</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2719.84</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-536.8400000000001</v>
+        <v>2319</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.245918460833715</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2922,13 +2922,13 @@
         <v>199.5</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>74.29000000000001</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>125.21</v>
+        <v>199.5</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.3723809523809524</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2963,20 +2963,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INODOROS</t>
+          <t>LAVABOS</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>240</v>
+        <v>347.55</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-321.11</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>561.11</v>
+        <v>347.55</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-1.337958333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2987,20 +2987,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LAVABOS</t>
+          <t>NO RESURTIBLES</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>432.29</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-169.29</v>
+        <v>250</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.643688212927757</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3011,17 +3011,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NO RESURTIBLES</t>
+          <t>OTROS</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -3035,17 +3035,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OTROS</t>
+          <t>PANELES DECORATIVOS</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0</v>
+        <v>528</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>528</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -3059,17 +3059,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PANELES DECORATIVOS</t>
+          <t>PANELES PVC Y PU</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>407</v>
+        <v>115</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>407</v>
+        <v>115</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0</v>
@@ -3083,20 +3083,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PANELES PVC Y PU</t>
+          <t>PIEDRA SINTERIZADA</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>115</v>
+        <v>3250</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>388.44</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-273.44</v>
+        <v>3250</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>3.377739130434783</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3107,20 +3107,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PIEDRA SINTERIZADA</t>
+          <t>PORCELANATO</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>467</v>
+        <v>30950</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>5403.61</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-4936.61</v>
+        <v>30950</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>11.57089935760171</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3131,20 +3131,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PORCELANATO</t>
+          <t>PUERTAS DE SEGURIDAD</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>52623</v>
+        <v>199.8</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>73049.53</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-20426.53</v>
+        <v>199.8</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.388167341276628</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3155,17 +3155,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PUERTAS DE SEGURIDAD</t>
+          <t>SAL SOLUBLE</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>199.8</v>
+        <v>0</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>199.8</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>0</v>
@@ -3178,16 +3178,16 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>57256.2</v>
+        <v>38331.67000000001</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>81746.89</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-24490.69</v>
+        <v>38331.67000000001</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1.427738655377059</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1800,7 +1800,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>0</v>
+        <v>740.59</v>
       </c>
       <c r="N22" s="2" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>0 de 24</t>
+          <t>1 de 24</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2099,7 +2099,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2701,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0</v>
+        <v>740.59</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
         <v>85825.07000000001</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0</v>
+        <v>740.59</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>49000</v>
@@ -2822,9 +2822,9 @@
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3114,13 +3114,13 @@
         <v>30950</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>740.59</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>30950</v>
+        <v>30209.41</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.02392859450726979</v>
       </c>
     </row>
     <row r="13">
@@ -3181,13 +3181,13 @@
         <v>38331.67000000001</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>740.59</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>38331.67000000001</v>
+        <v>37591.08</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0</v>
+        <v>0.0193205774754922</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>380.13</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>0</v>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>0 de 24</t>
+          <t>1 de 24</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
@@ -2296,7 +2296,7 @@
         <v>5824.86</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
+        <v>380.13</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>5000</v>
@@ -2799,7 +2799,7 @@
         <v>85825.07000000001</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>740.59</v>
+        <v>1120.72</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>49000</v>
@@ -3090,13 +3090,13 @@
         <v>3250</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>380.13</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3250</v>
+        <v>2869.87</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>0.1169630769230769</v>
       </c>
     </row>
     <row r="12">
@@ -3181,13 +3181,13 @@
         <v>38331.67000000001</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>740.59</v>
+        <v>1120.72</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>37591.08</v>
+        <v>37210.95</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.0193205774754922</v>
+        <v>0.02923744256381211</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>-41.65</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>5824.86</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>380.13</v>
+        <v>338.48</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>5000</v>
@@ -2799,7 +2799,7 @@
         <v>85825.07000000001</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>1120.72</v>
+        <v>1079.07</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>49000</v>
@@ -2970,13 +2970,13 @@
         <v>347.55</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>-41.65</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>347.55</v>
+        <v>389.2</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>-0.1198388721047331</v>
       </c>
     </row>
     <row r="7">
@@ -3181,13 +3181,13 @@
         <v>38331.67000000001</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1120.72</v>
+        <v>1079.07</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>37210.95</v>
+        <v>37252.60000000001</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.02923744256381211</v>
+        <v>0.02815087367704042</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1800,7 +1800,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>740.59</v>
+        <v>718.15</v>
       </c>
       <c r="N22" s="2" t="n">
         <v>0</v>
@@ -2701,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>740.59</v>
+        <v>718.15</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
         <v>85825.07000000001</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>1079.07</v>
+        <v>1056.63</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>49000</v>
@@ -3114,13 +3114,13 @@
         <v>30950</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>740.59</v>
+        <v>718.15</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>30209.41</v>
+        <v>30231.85</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.02392859450726979</v>
+        <v>0.02320355411954766</v>
       </c>
     </row>
     <row r="13">
@@ -3181,13 +3181,13 @@
         <v>38331.67000000001</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1079.07</v>
+        <v>1056.63</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>37252.60000000001</v>
+        <v>37275.04</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.02815087367704042</v>
+        <v>0.02756545697069812</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>0</v>
+        <v>-122.43</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0</v>
@@ -2099,7 +2099,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2620,7 +2620,7 @@
         <v>16038.62</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0</v>
+        <v>-122.43</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>5000</v>
@@ -2799,7 +2799,7 @@
         <v>85825.07000000001</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>1056.63</v>
+        <v>934.2</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>49000</v>
@@ -3114,13 +3114,13 @@
         <v>30950</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>718.15</v>
+        <v>595.72</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>30231.85</v>
+        <v>30354.28</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.02320355411954766</v>
+        <v>0.01924781906300485</v>
       </c>
     </row>
     <row r="13">
@@ -3181,13 +3181,13 @@
         <v>38331.67000000001</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1056.63</v>
+        <v>934.2</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>37275.04</v>
+        <v>37397.47</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.02756545697069812</v>
+        <v>0.02437149229344821</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>0</v>
+        <v>-23.39</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
         <v>21023.68</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0</v>
+        <v>-23.39</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>7000</v>
@@ -2799,7 +2799,7 @@
         <v>85825.07000000001</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>934.2</v>
+        <v>910.8099999999999</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>49000</v>
@@ -3114,13 +3114,13 @@
         <v>30950</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>595.72</v>
+        <v>572.33</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>30354.28</v>
+        <v>30377.67</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.01924781906300485</v>
+        <v>0.01849208400646204</v>
       </c>
     </row>
     <row r="13">
@@ -3181,13 +3181,13 @@
         <v>38331.67000000001</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>934.2</v>
+        <v>910.8100000000001</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>37397.47</v>
+        <v>37420.86</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.02437149229344821</v>
+        <v>0.02376129190301388</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>3231.36</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>1 de 24</t>
+          <t>2 de 24</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2350,7 +2350,7 @@
         <v>6156.27</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
+        <v>3231.36</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>5000</v>
@@ -2799,7 +2799,7 @@
         <v>85825.07000000001</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>910.8099999999999</v>
+        <v>4142.17</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>49000</v>
@@ -2822,7 +2822,7 @@
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3114,13 +3114,13 @@
         <v>30950</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>572.33</v>
+        <v>3803.69</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>30377.67</v>
+        <v>27146.31</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.01849208400646204</v>
+        <v>0.1228978998384491</v>
       </c>
     </row>
     <row r="13">
@@ -3181,13 +3181,13 @@
         <v>38331.67000000001</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>910.8100000000001</v>
+        <v>4142.17</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>37420.86</v>
+        <v>34189.5</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.02376129190301388</v>
+        <v>0.1080612976163052</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0</v>
+        <v>2356.99</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>2 de 24</t>
+          <t>3 de 24</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>2356.99</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>6500</v>
@@ -2799,7 +2799,7 @@
         <v>85825.07000000001</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>4142.17</v>
+        <v>6499.16</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>49000</v>
@@ -3114,13 +3114,13 @@
         <v>30950</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>3803.69</v>
+        <v>6160.68</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>27146.31</v>
+        <v>24789.32</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.1228978998384491</v>
+        <v>0.1990526655896608</v>
       </c>
     </row>
     <row r="13">
@@ -3181,13 +3181,13 @@
         <v>38331.67000000001</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>4142.17</v>
+        <v>6499.16</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>34189.5</v>
+        <v>31832.51</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.1080612976163052</v>
+        <v>0.169550661372176</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-41.65</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>380.13</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3231.36</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2356.99</v>
+        <v>0</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-122.43</v>
+        <v>0</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0</v>
@@ -1800,7 +1800,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>718.15</v>
+        <v>0</v>
       </c>
       <c r="N22" s="2" t="n">
         <v>0</v>
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-23.39</v>
+        <v>0</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>1 de 24</t>
+          <t>0 de 24</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>3 de 24</t>
+          <t>0 de 24</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2096,10 +2096,10 @@
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2116,22 +2116,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>enero</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2233,13 +2233,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>5457.09</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>6983.53</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6983.53</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
@@ -2287,16 +2287,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>3543.89</v>
+        <v>2875.17</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2875.17</v>
+        <v>5824.86</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>5824.86</v>
+        <v>338.48</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>338.48</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>5000</v>
@@ -2341,16 +2341,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3632.07</v>
+        <v>1202.95</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1202.95</v>
+        <v>6156.27</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>6156.27</v>
+        <v>3231.36</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>3231.36</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>5000</v>
@@ -2395,13 +2395,13 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2844.2</v>
+        <v>-45.68</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>-45.68</v>
+        <v>1769.26</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1769.26</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
@@ -2422,13 +2422,13 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>4438.42</v>
+        <v>1894.07</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1894.07</v>
+        <v>3457.21</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>3457.21</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
@@ -2452,10 +2452,10 @@
         <v>0</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>546.86</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>546.86</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>10228.49</v>
+        <v>1128.6</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1128.6</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0</v>
+        <v>2356.99</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>2356.99</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>6500</v>
@@ -2530,13 +2530,13 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>5818.17</v>
+        <v>7770.75</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7770.75</v>
+        <v>15970.38</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>15970.38</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>3539.95</v>
+        <v>1994.82</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1994.82</v>
+        <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0</v>
@@ -2611,16 +2611,16 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>6802.16</v>
+        <v>0</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>16038.62</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>16038.62</v>
+        <v>-122.43</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-122.43</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>5000</v>
@@ -2692,16 +2692,16 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>4415.8</v>
+        <v>0</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>718.15</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>718.15</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -2746,13 +2746,13 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>940.5</v>
+        <v>-1494</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>-1494</v>
+        <v>8054.4</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>8054.4</v>
+        <v>0</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
@@ -2773,16 +2773,16 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>2389</v>
+        <v>0</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0</v>
+        <v>21023.68</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>21023.68</v>
+        <v>-23.39</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-23.39</v>
+        <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>7000</v>
@@ -2790,16 +2790,16 @@
     </row>
     <row r="26">
       <c r="C26" s="6" t="n">
-        <v>54049.74</v>
+        <v>15326.68</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>15326.68</v>
+        <v>85825.07000000001</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>85825.07000000001</v>
+        <v>6499.16</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>6499.16</v>
+        <v>0</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>49000</v>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -2091,7 +2091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ANDINO RENDON ARACELY</t>
+          <t>ALMEIDA MIER SONIA MARINA</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BENAVIDES REVELO SILVIA PATRICIA</t>
+          <t>ANDINO RENDON ARACELY</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BENITEZ ANGAMARCA RICHARD EDISON</t>
+          <t>ARZA YAGUANA JUAN JOSÉ</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -2229,14 +2229,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CARRION CARRION LESLY ANABE</t>
+          <t>BENAVIDES REVELO GUSTAVO ALFONSO</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>6983.53</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
@@ -2245,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CARRION CARRION STEPHANIE DAYANA</t>
+          <t>BENAVIDES REVELO SILVIA PATRICIA</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -2283,23 +2283,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CHASIQUIZA CAMPAÑA JOSE LUIS</t>
+          <t>BENITEZ ANGAMARCA RICHARD EDISON</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>2875.17</v>
+        <v>0</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>5824.86</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>338.48</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2310,14 +2310,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CHONTASI SIMBAÑA SILVIA JANETH</t>
+          <t>CARRION CARRION LESLY ANABE</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>6983.53</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>0</v>
@@ -2326,7 +2326,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="9">
@@ -2337,23 +2337,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DECORHOME S.C.C.</t>
+          <t>CARRION CARRION STEPHANIE DAYANA</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1202.95</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>6156.27</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3231.36</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2364,23 +2364,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ESCUDERO CRUZ SILVIA RAQUEL</t>
+          <t>CHASIQUIZA CAMPAÑA JOSE LUIS</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0</v>
+        <v>2875.17</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>5824.86</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>338.48</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="11">
@@ -2391,14 +2391,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FERRETERIAS FERRIGONZ SA</t>
+          <t>CHAVEZ IMBAQUINGO EDGAR MAURICIO</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-45.68</v>
+        <v>0</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1769.26</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2418,14 +2418,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JARAMILLO CARVAJAL NICOLAS ESTEBAN</t>
+          <t>CHONTASI SIMBAÑA SILVIA JANETH</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1894.07</v>
+        <v>0</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>3457.21</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
@@ -2434,7 +2434,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>6000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="13">
@@ -2445,23 +2445,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MARIN DELGADO BRENDA MARIA</t>
+          <t>DECORHOME S.C.C.</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0</v>
+        <v>1202.95</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>546.86</v>
+        <v>6156.27</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>3231.36</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="14">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MATERIALES DE CONSTRUCCION SUPERMACONSVI S.A.</t>
+          <t>ESCUDERO CRUZ SILVIA RAQUEL</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -2499,23 +2499,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MEGAMAFERS S.A.</t>
+          <t>FERNANDEZ CEVALLOS JUAN CARLOS</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1128.6</v>
+        <v>0</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2356.99</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>6500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MUÑOZ LOZA ROMMEL SEBASTIAN</t>
+          <t>FERRETERIAS FERRIGONZ SA</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>7770.75</v>
+        <v>-45.68</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>15970.38</v>
+        <v>1769.26</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>0</v>
@@ -2542,7 +2542,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>6500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="17">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ORTEGA PAREDES RUDHT ELENA</t>
+          <t>GUERRA COLOMA ALEX SHUSEP</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -2580,11 +2580,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OÑATE PEREZ MERCY YOLANDA</t>
+          <t>IMPORTADORA VEGA S.A.</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1994.82</v>
+        <v>0</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>0</v>
@@ -2596,7 +2596,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2607,23 +2607,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PADILLA MIER BERTHA MARIETA</t>
+          <t>JARAMILLO CARVAJAL NICOLAS ESTEBAN</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0</v>
+        <v>1894.07</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>16038.62</v>
+        <v>3457.21</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-122.43</v>
+        <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>5000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="20">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PAVIMARSA S.A.</t>
+          <t>JARAMILLO ORDOÑEZ FREDDY ROBERTO</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>REA ARMAS CARLOS FERNANDO</t>
+          <t>JUMBO DIAZ MARCO ALCIDES</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -2688,17 +2688,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SARZOSA UNDA JOSE DOMINGO</t>
+          <t>MARIN DELGADO BRENDA MARIA</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>546.86</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>718.15</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SIGCHOS MORA FRANKLIN PORFIRIO</t>
+          <t>MATERIALES DE CONSTRUCCION SUPERMACONSVI S.A.</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -2742,23 +2742,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TRUJILLO TORRES VINICIO RUBEN</t>
+          <t>MEGAMAFERS S.A.</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>-1494</v>
+        <v>1128.6</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>8054.4</v>
+        <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0</v>
+        <v>2356.99</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="25">
@@ -2769,39 +2769,363 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>MELENDEZ PEREZ GRACIELA ALEXANDRA</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MORILLO CORRAL RUBI KATERINE</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MUÑOZ LOZA ROMMEL SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>7770.75</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>15970.38</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NUÑEZ MONGE CARLOS ALFREDO</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ORTEGA PAREDES RUDHT ELENA</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>OÑATE PEREZ MERCY YOLANDA</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>1994.82</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PADILLA MIER BERTHA MARIETA</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>16038.62</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>-122.43</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PAVIMARSA S.A.</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>RUIZ AGUDELO CESAR HERMOGENES</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SARZOSA UNDA JOSE DOMINGO</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>718.15</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SIGCHOS MORA FRANKLIN PORFIRIO</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>TRUJILLO TORRES VINICIO RUBEN</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>-1494</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>8054.4</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>TULCAN NARVAEZ EDITH MARITZA</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="2" t="n">
+      <c r="C37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2" t="n">
         <v>21023.68</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E37" s="2" t="n">
         <v>-23.39</v>
       </c>
-      <c r="F25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="2" t="n">
+      <c r="F37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="2" t="n">
         <v>7000</v>
       </c>
     </row>
-    <row r="26">
-      <c r="C26" s="6" t="n">
+    <row r="38">
+      <c r="C38" s="6" t="n">
         <v>15326.68</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D38" s="6" t="n">
         <v>85825.07000000001</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E38" s="6" t="n">
         <v>6499.16</v>
       </c>
-      <c r="F26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="6" t="n">
+      <c r="F38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="6" t="n">
         <v>49000</v>
       </c>
     </row>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FERRETERIAS FERRIGONZ SA</t>
+          <t>FERNANDEZ CEVALLOS JUAN CARLOS</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JARAMILLO CARVAJAL NICOLAS ESTEBAN</t>
+          <t>FERRETERIAS FERRIGONZ SA</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MARIN DELGADO BRENDA MARIA</t>
+          <t>IMPORTADORA VEGA S.A.</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MATERIALES DE CONSTRUCCION SUPERMACONSVI S.A.</t>
+          <t>JARAMILLO CARVAJAL NICOLAS ESTEBAN</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MEGAMAFERS S.A.</t>
+          <t>MARIN DELGADO BRENDA MARIA</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MUÑOZ LOZA ROMMEL SEBASTIAN</t>
+          <t>MATERIALES DE CONSTRUCCION SUPERMACONSVI S.A.</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ORTEGA PAREDES RUDHT ELENA</t>
+          <t>MEGAMAFERS S.A.</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OÑATE PEREZ MERCY YOLANDA</t>
+          <t>MORILLO CORRAL RUBI KATERINE</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PADILLA MIER BERTHA MARIETA</t>
+          <t>MUÑOZ LOZA ROMMEL SEBASTIAN</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PAVIMARSA S.A.</t>
+          <t>ORTEGA PAREDES RUDHT ELENA</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>REA ARMAS CARLOS FERNANDO</t>
+          <t>OÑATE PEREZ MERCY YOLANDA</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SARZOSA UNDA JOSE DOMINGO</t>
+          <t>PADILLA MIER BERTHA MARIETA</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SIGCHOS MORA FRANKLIN PORFIRIO</t>
+          <t>PAVIMARSA S.A.</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TRUJILLO TORRES VINICIO RUBEN</t>
+          <t>SARZOSA UNDA JOSE DOMINGO</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -1946,137 +1946,257 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>SIGCHOS MORA FRANKLIN PORFIRIO</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TRUJILLO TORRES VINICIO RUBEN</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>TULCAN NARVAEZ EDITH MARITZA</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="N26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="O26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="P26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="R26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
+      <c r="C27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>0 de 26</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>0 de 26</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>0 de 26</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>0 de 26</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>0 de 26</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>0 de 26</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>0 de 26</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>0 de 26</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>0 de 26</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>0 de 26</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>0 de 26</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>0 de 26</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>0 de 26</t>
+        </is>
+      </c>
+      <c r="P28" s="4" t="inlineStr">
+        <is>
+          <t>0 de 26</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="inlineStr">
+        <is>
+          <t>0 de 26</t>
+        </is>
+      </c>
+      <c r="R28" s="4" t="inlineStr">
+        <is>
+          <t>0 de 26</t>
         </is>
       </c>
     </row>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1320,7 +1320,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>0</v>
+        <v>5801.69</v>
       </c>
       <c r="N14" s="2" t="n">
         <v>0</v>
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>1049.93</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
@@ -1620,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>0</v>
+        <v>3027.2</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0</v>
+        <v>208.24</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>0</v>
@@ -2126,57 +2126,57 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
+          <t>1 de 26</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
           <t>0 de 26</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>0 de 26</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>0 de 26</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>0 de 26</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>0 de 26</t>
         </is>
       </c>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>0 de 26</t>
         </is>
       </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>0 de 26</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr">
+      <c r="L28" s="4" t="inlineStr">
         <is>
           <t>0 de 26</t>
         </is>
       </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>0 de 26</t>
-        </is>
-      </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>0 de 26</t>
+          <t>2 de 26</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>0 de 26</t>
+          <t>1 de 26</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
@@ -2219,7 +2219,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2740,7 +2740,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0</v>
+        <v>5801.69</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>6000</v>
@@ -2956,7 +2956,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0</v>
+        <v>4285.37</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>6500</v>
@@ -3243,7 +3243,7 @@
         <v>6499.16</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>0</v>
+        <v>10087.06</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>49000</v>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1320,7 +1320,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>5801.69</v>
+        <v>6446.13</v>
       </c>
       <c r="N14" s="2" t="n">
         <v>0</v>
@@ -2740,7 +2740,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>5801.69</v>
+        <v>6446.13</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>6000</v>
@@ -3037,7 +3037,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0</v>
+        <v>42.13</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>1500</v>
@@ -3243,7 +3243,7 @@
         <v>6499.16</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>10087.06</v>
+        <v>10773.63</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>49000</v>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>44.1</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0</v>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>0 de 26</t>
+          <t>1 de 26</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2497,7 +2497,7 @@
         <v>338.48</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
+        <v>46.71</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>5000</v>
@@ -3243,7 +3243,7 @@
         <v>6499.16</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>10773.63</v>
+        <v>10820.34</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>49000</v>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -3260,15 +3260,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3315,13 +3315,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>0</v>
@@ -3339,16 +3339,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2319</v>
+        <v>2450</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>1049.93</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2319</v>
+        <v>1400.07</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>0.4285428571428572</v>
       </c>
     </row>
     <row r="4">
@@ -3363,13 +3363,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>199.5</v>
+        <v>198</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>199.5</v>
+        <v>198</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
@@ -3387,13 +3387,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>172.82</v>
+        <v>133.5</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>172.82</v>
+        <v>133.5</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -3411,16 +3411,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>347.55</v>
+        <v>312</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-41.65</v>
+        <v>44.1</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>389.2</v>
+        <v>267.9</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.1198388721047331</v>
+        <v>0.1413461538461538</v>
       </c>
     </row>
     <row r="7">
@@ -3462,10 +3462,10 @@
         <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>-2.61</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -3483,13 +3483,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>528</v>
+        <v>400</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>528</v>
+        <v>400</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -3507,16 +3507,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>115</v>
+        <v>220</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>42.13</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>115</v>
+        <v>177.87</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>0.1915</v>
       </c>
     </row>
     <row r="11">
@@ -3531,16 +3531,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>3250</v>
+        <v>574</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>380.13</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2869.87</v>
+        <v>574</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1169630769230769</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3555,16 +3555,16 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>30950</v>
+        <v>53908</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6160.68</v>
+        <v>9473.33</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>24789.32</v>
+        <v>44434.67</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.1990526655896608</v>
+        <v>0.1757314313274468</v>
       </c>
     </row>
     <row r="13">
@@ -3579,59 +3579,35 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>199.8</v>
+        <v>228</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>208.24</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>199.8</v>
+        <v>19.75999999999999</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>0.9133333333333333</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SAL SOLUBLE</t>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0</v>
+        <v>58795.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>10820.34</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>47975.16</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>38331.67000000001</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>6499.16</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>31832.51</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>0.169550661372176</v>
+        <v>0.1840334719493839</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0</v>
+        <v>6757.39</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0</v>
+        <v>2349.95</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>2 de 26</t>
+          <t>4 de 26</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -2875,7 +2875,7 @@
         <v>2356.99</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0</v>
+        <v>6757.39</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>6500</v>
@@ -3037,7 +3037,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>42.13</v>
+        <v>2392.08</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>1500</v>
@@ -3243,7 +3243,7 @@
         <v>6499.16</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>10820.34</v>
+        <v>19927.68</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>49000</v>
@@ -3266,7 +3266,7 @@
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3558,13 +3558,13 @@
         <v>53908</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>9473.33</v>
+        <v>18580.67</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>44434.67</v>
+        <v>35327.33</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.1757314313274468</v>
+        <v>0.344673703346442</v>
       </c>
     </row>
     <row r="13">
@@ -3601,13 +3601,13 @@
         <v>58795.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>10820.34</v>
+        <v>19927.68</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>47975.16</v>
+        <v>38867.82</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.1840334719493839</v>
+        <v>0.3389320611271271</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -2470,7 +2470,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
+        <v>102.59</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>6499.16</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>19927.68</v>
+        <v>20030.27</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>49000</v>
@@ -3510,13 +3510,13 @@
         <v>220</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>42.13</v>
+        <v>144.72</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>177.87</v>
+        <v>75.28</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.1915</v>
+        <v>0.6578181818181819</v>
       </c>
     </row>
     <row r="11">
@@ -3601,13 +3601,13 @@
         <v>58795.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>19927.68</v>
+        <v>20030.27</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>38867.82</v>
+        <v>38765.23</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.3389320611271271</v>
+        <v>0.3406769225535968</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1320,7 +1320,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>6446.13</v>
+        <v>8179.9</v>
       </c>
       <c r="N14" s="2" t="n">
         <v>0</v>
@@ -2740,7 +2740,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>6446.13</v>
+        <v>8179.9</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>6000</v>
@@ -3243,7 +3243,7 @@
         <v>6499.16</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>20030.27</v>
+        <v>21764.04</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>49000</v>
@@ -3558,13 +3558,13 @@
         <v>53908</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>18580.67</v>
+        <v>20314.44</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>35327.33</v>
+        <v>33593.56</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.344673703346442</v>
+        <v>0.3768353491133041</v>
       </c>
     </row>
     <row r="13">
@@ -3601,13 +3601,13 @@
         <v>58795.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>20030.27</v>
+        <v>21764.04</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>38765.23</v>
+        <v>37031.46</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.3406769225535968</v>
+        <v>0.3701650636528306</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>44.1</v>
+        <v>220.5</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0</v>
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1049.93</v>
+        <v>3194.92</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
@@ -1920,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>0</v>
+        <v>10114.14</v>
       </c>
       <c r="N24" s="2" t="n">
         <v>0</v>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>4 de 26</t>
+          <t>5 de 26</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -2219,7 +2219,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2497,7 +2497,7 @@
         <v>338.48</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>46.71</v>
+        <v>223.11</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>5000</v>
@@ -2956,7 +2956,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>4285.37</v>
+        <v>6430.36</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>6500</v>
@@ -3145,7 +3145,7 @@
         <v>718.15</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0</v>
+        <v>10114.14</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>6499.16</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>21764.04</v>
+        <v>34199.57</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>49000</v>
@@ -3267,7 +3267,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -3342,13 +3342,13 @@
         <v>2450</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1049.93</v>
+        <v>3194.92</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1400.07</v>
+        <v>-744.9200000000001</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.4285428571428572</v>
+        <v>1.304048979591837</v>
       </c>
     </row>
     <row r="4">
@@ -3414,13 +3414,13 @@
         <v>312</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>44.1</v>
+        <v>220.5</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>267.9</v>
+        <v>91.5</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1413461538461538</v>
+        <v>0.7067307692307693</v>
       </c>
     </row>
     <row r="7">
@@ -3558,13 +3558,13 @@
         <v>53908</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>20314.44</v>
+        <v>30428.58</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>33593.56</v>
+        <v>23479.42</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.3768353491133041</v>
+        <v>0.564453884395637</v>
       </c>
     </row>
     <row r="13">
@@ -3601,13 +3601,13 @@
         <v>58795.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>21764.04</v>
+        <v>34199.57</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>37031.46</v>
+        <v>24595.93</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.3701650636528306</v>
+        <v>0.5816698556862345</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3027.2</v>
+        <v>11731.35</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>208.24</v>
@@ -2956,7 +2956,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>6430.36</v>
+        <v>15134.51</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>6500</v>
@@ -3243,7 +3243,7 @@
         <v>6499.16</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>34199.57</v>
+        <v>42903.72</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>49000</v>
@@ -3558,13 +3558,13 @@
         <v>53908</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>30428.58</v>
+        <v>39132.73</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>23479.42</v>
+        <v>14775.27</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.564453884395637</v>
+        <v>0.7259169325517549</v>
       </c>
     </row>
     <row r="13">
@@ -3601,13 +3601,13 @@
         <v>58795.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>34199.57</v>
+        <v>42903.72</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>24595.93</v>
+        <v>15891.78</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.5816698556862345</v>
+        <v>0.7297109472663724</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>220.5</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0</v>
@@ -1320,7 +1320,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8179.9</v>
+        <v>0</v>
       </c>
       <c r="N14" s="2" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>6757.39</v>
+        <v>0</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>3194.92</v>
+        <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
@@ -1620,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>11731.35</v>
+        <v>0</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>208.24</v>
+        <v>0</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>0</v>
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2349.95</v>
+        <v>0</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -1920,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>10114.14</v>
+        <v>0</v>
       </c>
       <c r="N24" s="2" t="n">
         <v>0</v>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>1 de 26</t>
+          <t>0 de 26</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>1 de 26</t>
+          <t>0 de 26</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>5 de 26</t>
+          <t>0 de 26</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>1 de 26</t>
+          <t>0 de 26</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
@@ -2216,10 +2216,10 @@
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2236,22 +2236,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0</v>
+        <v>6983.53</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>6983.53</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>0</v>
@@ -2467,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>102.59</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>102.59</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -2488,16 +2488,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2875.17</v>
+        <v>5824.86</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>5824.86</v>
+        <v>338.48</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>338.48</v>
+        <v>12910.91</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>223.11</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>5000</v>
@@ -2569,13 +2569,13 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1202.95</v>
+        <v>6156.27</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6156.27</v>
+        <v>3231.36</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>3231.36</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-45.68</v>
+        <v>1769.26</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1769.26</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>0</v>
@@ -2731,16 +2731,16 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>1894.07</v>
+        <v>3457.21</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>3457.21</v>
+        <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0</v>
+        <v>10650.37</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>8179.9</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>6000</v>
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0</v>
+        <v>546.86</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>546.86</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0</v>
@@ -2866,16 +2866,16 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>1128.6</v>
+        <v>0</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0</v>
+        <v>2356.99</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>2356.99</v>
+        <v>6938.84</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>6757.39</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>6500</v>
@@ -2947,16 +2947,16 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>7770.75</v>
+        <v>15970.38</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>15970.38</v>
+        <v>0</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0</v>
+        <v>15134.51</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>15134.51</v>
+        <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>6500</v>
@@ -3028,16 +3028,16 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>1994.82</v>
+        <v>0</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0</v>
+        <v>2392.08</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>2392.08</v>
+        <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>1500</v>
@@ -3055,13 +3055,13 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>0</v>
+        <v>16038.62</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>16038.62</v>
+        <v>-122.43</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-122.43</v>
+        <v>0</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>0</v>
@@ -3139,13 +3139,13 @@
         <v>0</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0</v>
+        <v>718.15</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>718.15</v>
+        <v>10114.14</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>10114.14</v>
+        <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>0</v>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>-1494</v>
+        <v>8054.4</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>8054.4</v>
+        <v>0</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>0</v>
@@ -3217,13 +3217,13 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>0</v>
+        <v>21023.68</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>21023.68</v>
+        <v>-23.39</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>-23.39</v>
+        <v>0</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>0</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="38">
       <c r="C38" s="6" t="n">
-        <v>15326.68</v>
+        <v>85825.07000000001</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>85825.07000000001</v>
+        <v>6499.16</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>6499.16</v>
+        <v>58243.44</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>42903.72</v>
+        <v>0</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>49000</v>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0</v>
+        <v>6.69</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>0 de 26</t>
+          <t>1 de 26</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -3037,7 +3037,7 @@
         <v>2392.08</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0</v>
+        <v>6.69</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>1500</v>
@@ -3243,7 +3243,7 @@
         <v>58243.44</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>0</v>
+        <v>6.69</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>49000</v>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:R27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IMPORTADORA VEGA S.A.</t>
+          <t>JARAMILLO CARVAJAL NICOLAS ESTEBAN</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JARAMILLO CARVAJAL NICOLAS ESTEBAN</t>
+          <t>MARIN DELGADO BRENDA MARIA</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MARIN DELGADO BRENDA MARIA</t>
+          <t>MATERIALES DE CONSTRUCCION SUPERMACONSVI S.A.</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MATERIALES DE CONSTRUCCION SUPERMACONSVI S.A.</t>
+          <t>MEGAMAFERS S.A.</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MEGAMAFERS S.A.</t>
+          <t>MORILLO CORRAL RUBI KATERINE</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MORILLO CORRAL RUBI KATERINE</t>
+          <t>MUÑOZ LOZA ROMMEL SEBASTIAN</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MUÑOZ LOZA ROMMEL SEBASTIAN</t>
+          <t>ORTEGA PAREDES RUDHT ELENA</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ORTEGA PAREDES RUDHT ELENA</t>
+          <t>OÑATE PEREZ MERCY YOLANDA</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>0</v>
+        <v>6.69</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>OÑATE PEREZ MERCY YOLANDA</t>
+          <t>PADILLA MIER BERTHA MARIETA</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>6.69</v>
+        <v>0</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PADILLA MIER BERTHA MARIETA</t>
+          <t>PAVIMARSA S.A.</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PAVIMARSA S.A.</t>
+          <t>SARZOSA UNDA JOSE DOMINGO</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SARZOSA UNDA JOSE DOMINGO</t>
+          <t>SIGCHOS MORA FRANKLIN PORFIRIO</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SIGCHOS MORA FRANKLIN PORFIRIO</t>
+          <t>TRUJILLO TORRES VINICIO RUBEN</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TRUJILLO TORRES VINICIO RUBEN</t>
+          <t>TULCAN NARVAEZ EDITH MARITZA</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -2059,144 +2059,84 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>TULCAN NARVAEZ EDITH MARITZA</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>0 de 26</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>0 de 26</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>0 de 26</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>0 de 26</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>0 de 26</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>0 de 26</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>0 de 26</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>0 de 26</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>0 de 26</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>0 de 26</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>1 de 26</t>
-        </is>
-      </c>
-      <c r="N28" s="4" t="inlineStr">
-        <is>
-          <t>0 de 26</t>
-        </is>
-      </c>
-      <c r="O28" s="4" t="inlineStr">
-        <is>
-          <t>0 de 26</t>
-        </is>
-      </c>
-      <c r="P28" s="4" t="inlineStr">
-        <is>
-          <t>0 de 26</t>
-        </is>
-      </c>
-      <c r="Q28" s="4" t="inlineStr">
-        <is>
-          <t>0 de 26</t>
-        </is>
-      </c>
-      <c r="R28" s="4" t="inlineStr">
-        <is>
-          <t>0 de 26</t>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>1 de 25</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="P27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="Q27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="R27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
         </is>
       </c>
     </row>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1428,7 +1428,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>-97.2</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>0</v>
@@ -2159,7 +2159,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2815,7 +2815,7 @@
         <v>6938.84</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0</v>
+        <v>-181.45</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>6500</v>
@@ -3183,7 +3183,7 @@
         <v>58243.44</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>6.69</v>
+        <v>-174.76</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>49000</v>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>46.47</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>0</v>
+        <v>241.55</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
@@ -2091,27 +2091,27 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
+          <t>1 de 25</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="L27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>1 de 25</t>
+          <t>2 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2680,7 +2680,7 @@
         <v>10650.37</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0</v>
+        <v>46.47</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>6000</v>
@@ -2896,7 +2896,7 @@
         <v>15134.51</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0</v>
+        <v>241.55</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>6500</v>
@@ -3183,7 +3183,7 @@
         <v>58243.44</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>-174.76</v>
+        <v>113.26</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>49000</v>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -3200,15 +3200,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3255,13 +3255,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>122</v>
+        <v>500</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>122</v>
+        <v>500</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>0</v>
@@ -3282,13 +3282,13 @@
         <v>2450</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3194.92</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-744.9200000000001</v>
+        <v>2450</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.304048979591837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3354,13 +3354,13 @@
         <v>312</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>220.5</v>
+        <v>-50.73</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>91.5</v>
+        <v>362.73</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.7067307692307693</v>
+        <v>-0.1625961538461538</v>
       </c>
     </row>
     <row r="7">
@@ -3402,10 +3402,10 @@
         <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-2.61</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -3450,13 +3450,13 @@
         <v>220</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>144.72</v>
+        <v>-84.25</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>75.28</v>
+        <v>304.25</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.6578181818181819</v>
+        <v>-0.3829545454545454</v>
       </c>
     </row>
     <row r="11">
@@ -3467,20 +3467,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PIEDRA SINTERIZADA</t>
+          <t>PORCELANATO</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>574</v>
+        <v>43400</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>248.24</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>574</v>
+        <v>43151.76</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>0.005719815668202765</v>
       </c>
     </row>
     <row r="12">
@@ -3491,63 +3491,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PORCELANATO</t>
+          <t>PUERTAS DE SEGURIDAD</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>53908</v>
+        <v>570</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>39132.73</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>14775.27</v>
+        <v>570</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.7259169325517549</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>PUERTAS DE SEGURIDAD</t>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>228</v>
+        <v>48433.5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>208.24</v>
+        <v>113.26</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>19.75999999999999</v>
+        <v>48320.24000000001</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9133333333333333</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>58795.5</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>42903.72</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>15891.78</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>0.7297109472663724</v>
+        <v>0.002338464079614317</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>-44.1</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>12910.91</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
+        <v>-44.1</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>5000</v>
@@ -3183,7 +3183,7 @@
         <v>58243.44</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>113.26</v>
+        <v>69.16000000000003</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>49000</v>
@@ -3354,13 +3354,13 @@
         <v>312</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-50.73</v>
+        <v>-94.83</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>362.73</v>
+        <v>406.83</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.1625961538461538</v>
+        <v>-0.3039423076923077</v>
       </c>
     </row>
     <row r="7">
@@ -3517,13 +3517,13 @@
         <v>48433.5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>113.26</v>
+        <v>69.16000000000003</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>48320.24000000001</v>
+        <v>48364.34</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.002338464079614317</v>
+        <v>0.001427937274820115</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>0</v>
+        <v>6.32</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>0</v>
+        <v>6.32</v>
       </c>
       <c r="N16" s="2" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>2 de 25</t>
+          <t>4 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2680,7 +2680,7 @@
         <v>10650.37</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>46.47</v>
+        <v>52.79</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>6000</v>
@@ -2815,7 +2815,7 @@
         <v>6938.84</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-181.45</v>
+        <v>-175.13</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>6500</v>
@@ -3183,7 +3183,7 @@
         <v>58243.44</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>69.16000000000003</v>
+        <v>81.80000000000001</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>49000</v>
@@ -3474,13 +3474,13 @@
         <v>43400</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>248.24</v>
+        <v>260.88</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>43151.76</v>
+        <v>43139.12</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.005719815668202765</v>
+        <v>0.006011059907834101</v>
       </c>
     </row>
     <row r="12">
@@ -3517,13 +3517,13 @@
         <v>48433.5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>69.16000000000003</v>
+        <v>81.80000000000001</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>48364.34</v>
+        <v>48351.7</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.001427937274820115</v>
+        <v>0.001688913665128475</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7">
@@ -2386,7 +2386,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>5000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="9">
@@ -2494,7 +2494,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2521,7 +2521,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="14">
@@ -2683,7 +2683,7 @@
         <v>52.79</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>6000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="20">
@@ -2818,7 +2818,7 @@
         <v>-175.13</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>6500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="25">
@@ -2899,7 +2899,7 @@
         <v>241.55</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>6500</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="28">
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="35">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="37">
@@ -3169,7 +3169,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>7000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="38">
@@ -3186,7 +3186,7 @@
         <v>81.80000000000001</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>49000</v>
+        <v>48500</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>6.32</v>
+        <v>38.54</v>
       </c>
       <c r="N16" s="2" t="n">
         <v>0</v>
@@ -2815,7 +2815,7 @@
         <v>6938.84</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-175.13</v>
+        <v>-142.91</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>5000</v>
@@ -3183,7 +3183,7 @@
         <v>58243.44</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>81.80000000000001</v>
+        <v>114.02</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>48500</v>
@@ -3474,13 +3474,13 @@
         <v>43400</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>260.88</v>
+        <v>293.1</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>43139.12</v>
+        <v>43106.9</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.006011059907834101</v>
+        <v>0.006753456221198158</v>
       </c>
     </row>
     <row r="12">
@@ -3517,13 +3517,13 @@
         <v>48433.5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>81.80000000000001</v>
+        <v>114.02</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>48351.7</v>
+        <v>48319.48</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.001688913665128475</v>
+        <v>0.002354155698018934</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -2151,7 +2151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -3045,23 +3045,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RUIZ AGUDELO CESAR HERMOGENES</t>
+          <t>SARZOSA UNDA JOSE DOMINGO</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0</v>
+        <v>718.15</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0</v>
+        <v>10114.14</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="34">
@@ -3072,23 +3072,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SARZOSA UNDA JOSE DOMINGO</t>
+          <t>SIGCHOS MORA FRANKLIN PORFIRIO</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>718.15</v>
+        <v>0</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>10114.14</v>
+        <v>0</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3099,11 +3099,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SIGCHOS MORA FRANKLIN PORFIRIO</t>
+          <t>TRUJILLO TORRES VINICIO RUBEN</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>0</v>
+        <v>8054.4</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>0</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="36">
@@ -3126,14 +3126,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TRUJILLO TORRES VINICIO RUBEN</t>
+          <t>TULCAN NARVAEZ EDITH MARITZA</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>8054.4</v>
+        <v>21023.68</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0</v>
+        <v>-23.39</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>0</v>
@@ -3142,50 +3142,23 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>3500</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>TULCAN NARVAEZ EDITH MARITZA</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>21023.68</v>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>-23.39</v>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>5500</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="C38" s="6" t="n">
+      <c r="C37" s="6" t="n">
         <v>85825.07000000001</v>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D37" s="6" t="n">
         <v>6499.16</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="E37" s="6" t="n">
         <v>58243.44</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="F37" s="6" t="n">
         <v>114.02</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="G37" s="6" t="n">
         <v>48500</v>
       </c>
     </row>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -2151,7 +2151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ALMEIDA MIER SONIA MARINA</t>
+          <t>ANDINO RENDON ARACELY</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ANDINO RENDON ARACELY</t>
+          <t>BENAVIDES REVELO SILVIA PATRICIA</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="4">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ARZA YAGUANA JUAN JOSÉ</t>
+          <t>BENITEZ ANGAMARCA RICHARD EDISON</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -2289,11 +2289,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BENAVIDES REVELO GUSTAVO ALFONSO</t>
+          <t>CARRION CARRION LESLY ANABE</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0</v>
+        <v>6983.53</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
@@ -2305,7 +2305,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="6">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BENAVIDES REVELO SILVIA PATRICIA</t>
+          <t>CARRION CARRION STEPHANIE DAYANA</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>102.59</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2343,23 +2343,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BENITEZ ANGAMARCA RICHARD EDISON</t>
+          <t>CHASIQUIZA CAMPAÑA JOSE LUIS</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0</v>
+        <v>5824.86</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>338.48</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>12910.91</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
+        <v>-44.1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="8">
@@ -2370,11 +2370,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CARRION CARRION LESLY ANABE</t>
+          <t>CHAVEZ IMBAQUINGO EDGAR MAURICIO</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>6983.53</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0</v>
@@ -2386,7 +2386,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CARRION CARRION STEPHANIE DAYANA</t>
+          <t>CHONTASI SIMBAÑA SILVIA JANETH</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>102.59</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
@@ -2424,23 +2424,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CHASIQUIZA CAMPAÑA JOSE LUIS</t>
+          <t>DECORHOME S.C.C.</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>5824.86</v>
+        <v>6156.27</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>338.48</v>
+        <v>3231.36</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>12910.91</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-44.1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="11">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CHAVEZ IMBAQUINGO EDGAR MAURICIO</t>
+          <t>ESCUDERO CRUZ SILVIA RAQUEL</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CHONTASI SIMBAÑA SILVIA JANETH</t>
+          <t>FERNANDEZ CEVALLOS JUAN CARLOS</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -2505,14 +2505,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DECORHOME S.C.C.</t>
+          <t>FERRETERIAS FERRIGONZ SA</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>6156.27</v>
+        <v>1769.26</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>3231.36</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="14">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ESCUDERO CRUZ SILVIA RAQUEL</t>
+          <t>IMPORTADORA VEGA S.A.</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -2559,23 +2559,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FERNANDEZ CEVALLOS JUAN CARLOS</t>
+          <t>JARAMILLO CARVAJAL NICOLAS ESTEBAN</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0</v>
+        <v>3457.21</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0</v>
+        <v>10650.37</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>52.79</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="16">
@@ -2586,11 +2586,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FERRETERIAS FERRIGONZ SA</t>
+          <t>MARIN DELGADO BRENDA MARIA</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1769.26</v>
+        <v>546.86</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GUERRA COLOMA ALEX SHUSEP</t>
+          <t>MATERIALES DE CONSTRUCCION SUPERMACONSVI S.A.</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -2640,23 +2640,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IMPORTADORA VEGA S.A.</t>
+          <t>MEGAMAFERS S.A.</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
+        <v>2356.99</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0</v>
+        <v>6938.84</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0</v>
+        <v>-142.91</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="19">
@@ -2667,23 +2667,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JARAMILLO CARVAJAL NICOLAS ESTEBAN</t>
+          <t>MUÑOZ LOZA ROMMEL SEBASTIAN</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>3457.21</v>
+        <v>15970.38</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>10650.37</v>
+        <v>15134.51</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>52.79</v>
+        <v>241.55</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>5000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="20">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JARAMILLO ORDOÑEZ FREDDY ROBERTO</t>
+          <t>ORTEGA PAREDES RUDHT ELENA</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JUMBO DIAZ MARCO ALCIDES</t>
+          <t>OÑATE PEREZ MERCY YOLANDA</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -2731,13 +2731,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0</v>
+        <v>2392.08</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0</v>
+        <v>6.69</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="22">
@@ -2748,14 +2748,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MARIN DELGADO BRENDA MARIA</t>
+          <t>PADILLA MIER BERTHA MARIETA</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>546.86</v>
+        <v>16038.62</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>-122.43</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0</v>
@@ -2764,7 +2764,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="23">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MATERIALES DE CONSTRUCCION SUPERMACONSVI S.A.</t>
+          <t>PAVIMARSA S.A.</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -2802,23 +2802,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MEGAMAFERS S.A.</t>
+          <t>SARZOSA UNDA JOSE DOMINGO</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>2356.99</v>
+        <v>718.15</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>6938.84</v>
+        <v>10114.14</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-142.91</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="25">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MELENDEZ PEREZ GRACIELA ALEXANDRA</t>
+          <t>SIGCHOS MORA FRANKLIN PORFIRIO</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -2856,11 +2856,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MORILLO CORRAL RUBI KATERINE</t>
+          <t>TRUJILLO TORRES VINICIO RUBEN</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0</v>
+        <v>8054.4</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>0</v>
@@ -2872,7 +2872,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="27">
@@ -2883,282 +2883,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MUÑOZ LOZA ROMMEL SEBASTIAN</t>
+          <t>TULCAN NARVAEZ EDITH MARITZA</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>15970.38</v>
+        <v>21023.68</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0</v>
+        <v>-23.39</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>15134.51</v>
+        <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>241.55</v>
+        <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>6000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>NUÑEZ MONGE CARLOS ALFREDO</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>ORTEGA PAREDES RUDHT ELENA</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>OÑATE PEREZ MERCY YOLANDA</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>2392.08</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>6.69</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>PADILLA MIER BERTHA MARIETA</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>16038.62</v>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>-122.43</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>PAVIMARSA S.A.</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>SARZOSA UNDA JOSE DOMINGO</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>718.15</v>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>10114.14</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>SIGCHOS MORA FRANKLIN PORFIRIO</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>TRUJILLO TORRES VINICIO RUBEN</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>8054.4</v>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>TULCAN NARVAEZ EDITH MARITZA</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>21023.68</v>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>-23.39</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>5500</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" s="6" t="n">
+      <c r="C28" s="6" t="n">
         <v>85825.07000000001</v>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D28" s="6" t="n">
         <v>6499.16</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="E28" s="6" t="n">
         <v>58243.44</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="F28" s="6" t="n">
         <v>114.02</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="G28" s="6" t="n">
         <v>48500</v>
       </c>
     </row>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>6.32</v>
+        <v>21.8</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -1428,7 +1428,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-97.2</v>
+        <v>122.11</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>1 de 25</t>
+          <t>2 de 25</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2159,7 +2159,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2572,7 +2572,7 @@
         <v>10650.37</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>52.79</v>
+        <v>68.27</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>5000</v>
@@ -2653,7 +2653,7 @@
         <v>6938.84</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-142.91</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>5000</v>
@@ -2913,7 +2913,7 @@
         <v>58243.44</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>114.02</v>
+        <v>348.81</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -3084,13 +3084,13 @@
         <v>312</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-94.83</v>
+        <v>124.48</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>406.83</v>
+        <v>187.52</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.3039423076923077</v>
+        <v>0.398974358974359</v>
       </c>
     </row>
     <row r="7">
@@ -3204,13 +3204,13 @@
         <v>43400</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>293.1</v>
+        <v>308.58</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>43106.9</v>
+        <v>43091.42</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.006753456221198158</v>
+        <v>0.007110138248847926</v>
       </c>
     </row>
     <row r="12">
@@ -3247,13 +3247,13 @@
         <v>48433.5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>114.02</v>
+        <v>348.81</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>48319.48</v>
+        <v>48084.69</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.002354155698018934</v>
+        <v>0.007201833441729382</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>6.69</v>
+        <v>323.61</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
@@ -2734,7 +2734,7 @@
         <v>2392.08</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>6.69</v>
+        <v>334.04</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>1500</v>
@@ -2913,7 +2913,7 @@
         <v>58243.44</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>348.81</v>
+        <v>676.1600000000001</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -2938,7 +2938,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3132,10 +3132,10 @@
         <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>10.43</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>-10.43</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -3204,13 +3204,13 @@
         <v>43400</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>308.58</v>
+        <v>625.5</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>43091.42</v>
+        <v>42774.5</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.007110138248847926</v>
+        <v>0.01441244239631336</v>
       </c>
     </row>
     <row r="12">
@@ -3247,13 +3247,13 @@
         <v>48433.5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>348.81</v>
+        <v>676.16</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>48084.69</v>
+        <v>47757.34</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.007201833441729382</v>
+        <v>0.01396058513219156</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>21.8</v>
+        <v>2870.38</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -1428,7 +1428,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>122.11</v>
+        <v>170.9</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>241.55</v>
+        <v>5291.29</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>323.61</v>
+        <v>1036.67</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
@@ -2159,7 +2159,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2572,7 +2572,7 @@
         <v>10650.37</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>68.27</v>
+        <v>2916.85</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>5000</v>
@@ -2653,7 +2653,7 @@
         <v>6938.84</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>76.40000000000001</v>
+        <v>125.19</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>5000</v>
@@ -2680,7 +2680,7 @@
         <v>15134.51</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>241.55</v>
+        <v>5291.29</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>6000</v>
@@ -2734,7 +2734,7 @@
         <v>2392.08</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>334.04</v>
+        <v>1047.1</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>1500</v>
@@ -2913,7 +2913,7 @@
         <v>58243.44</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>676.1600000000001</v>
+        <v>9336.33</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -2936,7 +2936,7 @@
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3084,13 +3084,13 @@
         <v>312</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>124.48</v>
+        <v>173.27</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>187.52</v>
+        <v>138.73</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.398974358974359</v>
+        <v>0.5553525641025642</v>
       </c>
     </row>
     <row r="7">
@@ -3204,13 +3204,13 @@
         <v>43400</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>625.5</v>
+        <v>9236.879999999999</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>42774.5</v>
+        <v>34163.12</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.01441244239631336</v>
+        <v>0.2128313364055299</v>
       </c>
     </row>
     <row r="12">
@@ -3247,13 +3247,13 @@
         <v>48433.5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>676.16</v>
+        <v>9336.33</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>47757.34</v>
+        <v>39097.17000000001</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.01396058513219156</v>
+        <v>0.1927659574468085</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>6.32</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>5291.29</v>
+        <v>7791.96</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>4 de 25</t>
+          <t>5 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2356,7 +2356,7 @@
         <v>12910.91</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-44.1</v>
+        <v>-37.78</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>5000</v>
@@ -2680,7 +2680,7 @@
         <v>15134.51</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>5291.29</v>
+        <v>7791.96</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>6000</v>
@@ -2913,7 +2913,7 @@
         <v>58243.44</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>9336.33</v>
+        <v>11843.32</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -2936,7 +2936,7 @@
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3204,13 +3204,13 @@
         <v>43400</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>9236.879999999999</v>
+        <v>11743.87</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>34163.12</v>
+        <v>31656.13</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.2128313364055299</v>
+        <v>0.2705960829493088</v>
       </c>
     </row>
     <row r="12">
@@ -3247,13 +3247,13 @@
         <v>48433.5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>9336.33</v>
+        <v>11843.32</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>39097.17000000001</v>
+        <v>36590.18</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.1927659574468085</v>
+        <v>0.2445274448470584</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-44.1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0</v>
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>6.32</v>
+        <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>46.47</v>
+        <v>0</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2870.38</v>
+        <v>0</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -1428,7 +1428,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>170.9</v>
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>38.54</v>
+        <v>0</v>
       </c>
       <c r="N16" s="2" t="n">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7791.96</v>
+        <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1036.67</v>
+        <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>2 de 25</t>
+          <t>0 de 25</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>5 de 25</t>
+          <t>0 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2156,10 +2156,10 @@
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2176,22 +2176,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>6983.53</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
@@ -2323,10 +2323,10 @@
         <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>102.59</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>102.59</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -2347,16 +2347,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>5824.86</v>
+        <v>338.48</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>338.48</v>
+        <v>12910.91</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>12910.91</v>
+        <v>-37.78</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-37.78</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>5000</v>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>6156.27</v>
+        <v>3231.36</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>3231.36</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
@@ -2509,7 +2509,7 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1769.26</v>
+        <v>0</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0</v>
@@ -2563,16 +2563,16 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>3457.21</v>
+        <v>0</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>10650.37</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>10650.37</v>
+        <v>2916.85</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>2916.85</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>5000</v>
@@ -2590,7 +2590,7 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>546.86</v>
+        <v>0</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>0</v>
@@ -2644,16 +2644,16 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0</v>
+        <v>2356.99</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>2356.99</v>
+        <v>6938.84</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>6938.84</v>
+        <v>125.19</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>125.19</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>5000</v>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>15970.38</v>
+        <v>0</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>15134.51</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>15134.51</v>
+        <v>7791.96</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>7791.96</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>6000</v>
@@ -2728,13 +2728,13 @@
         <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0</v>
+        <v>2392.08</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2392.08</v>
+        <v>1047.1</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1047.1</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>1500</v>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>16038.62</v>
+        <v>-122.43</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>-122.43</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0</v>
@@ -2806,13 +2806,13 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0</v>
+        <v>718.15</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>718.15</v>
+        <v>10114.14</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>10114.14</v>
+        <v>0</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>8054.4</v>
+        <v>0</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>0</v>
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>21023.68</v>
+        <v>-23.39</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>-23.39</v>
+        <v>0</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>0</v>
@@ -2904,16 +2904,16 @@
     </row>
     <row r="28">
       <c r="C28" s="6" t="n">
-        <v>85825.07000000001</v>
+        <v>6499.16</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>6499.16</v>
+        <v>58243.44</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>58243.44</v>
+        <v>11843.32</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>11843.32</v>
+        <v>0</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -2930,15 +2930,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2985,13 +2985,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>500</v>
+        <v>136.08</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>500</v>
+        <v>136.08</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>0</v>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2450</v>
+        <v>2183</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2450</v>
+        <v>2183</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
@@ -3033,13 +3033,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>198</v>
+        <v>199.5</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>198</v>
+        <v>199.5</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
@@ -3057,13 +3057,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>133.5</v>
+        <v>172.82</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>133.5</v>
+        <v>172.82</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -3081,16 +3081,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>312</v>
+        <v>263</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>173.27</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>138.73</v>
+        <v>263</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.5553525641025642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3132,10 +3132,10 @@
         <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>10.43</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-10.43</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -3153,13 +3153,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -3177,16 +3177,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>220</v>
+        <v>115</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>-84.25</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>304.25</v>
+        <v>115</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-0.3829545454545454</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -3197,20 +3197,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PORCELANATO</t>
+          <t>PIEDRA SINTERIZADA</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>43400</v>
+        <v>467</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>11743.87</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>31656.13</v>
+        <v>467</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.2705960829493088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3221,39 +3221,63 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>PORCELANATO</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>30623</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>30623</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>PUERTAS DE SEGURIDAD</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>570</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>570</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="7" t="inlineStr">
+      <c r="C13" s="2" t="n">
+        <v>199.8</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>199.8</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>48433.5</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>11843.32</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>36590.18</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>0.2445274448470584</v>
+      <c r="C14" s="2" t="n">
+        <v>35016.2</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>35016.2</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -780,7 +780,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0</v>
+        <v>2162.71</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>0</v>
@@ -840,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0</v>
+        <v>1812.75</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>0 de 25</t>
+          <t>2 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2159,7 +2159,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2302,7 +2302,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0</v>
+        <v>2162.71</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>4000</v>
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0</v>
+        <v>1812.75</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
@@ -2913,7 +2913,7 @@
         <v>11843.32</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0</v>
+        <v>3975.46</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -2936,9 +2936,9 @@
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3228,13 +3228,13 @@
         <v>30623</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>3975.46</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>30623</v>
+        <v>26647.54</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.1298194167782386</v>
       </c>
     </row>
     <row r="13">
@@ -3271,13 +3271,13 @@
         <v>35016.2</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>3975.46</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>35016.2</v>
+        <v>31040.74</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0</v>
+        <v>0.1135320223210971</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>2159.81</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>3502.7</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -1194,7 +1194,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>605.85</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1533,7 +1533,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
+        <v>1079.91</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0</v>
@@ -2066,52 +2066,52 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
+          <t>2 de 25</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>1 de 25</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>2 de 25</t>
+          <t>3 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2356,7 +2356,7 @@
         <v>-37.78</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
+        <v>2159.81</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>5000</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
+        <v>3502.7</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>3000</v>
@@ -2518,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0</v>
+        <v>605.85</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>1000</v>
@@ -2680,7 +2680,7 @@
         <v>7791.96</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0</v>
+        <v>1079.91</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>6000</v>
@@ -2913,7 +2913,7 @@
         <v>11843.32</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>3975.46</v>
+        <v>11323.73</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -3012,13 +3012,13 @@
         <v>2183</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>3239.72</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2183</v>
+        <v>-1056.72</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>1.484067796610169</v>
       </c>
     </row>
     <row r="4">
@@ -3156,13 +3156,13 @@
         <v>407</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>605.85</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>407</v>
+        <v>-198.85</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>1.488574938574939</v>
       </c>
     </row>
     <row r="10">
@@ -3228,13 +3228,13 @@
         <v>30623</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>3975.46</v>
+        <v>7478.16</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>26647.54</v>
+        <v>23144.84</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.1298194167782386</v>
+        <v>0.2442007641315351</v>
       </c>
     </row>
     <row r="13">
@@ -3271,13 +3271,13 @@
         <v>35016.2</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>3975.46</v>
+        <v>11323.73</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>31040.74</v>
+        <v>23692.47</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.1135320223210971</v>
+        <v>0.3233854615863514</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2159.81</v>
+        <v>3239.72</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
         <v>-37.78</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2159.81</v>
+        <v>3239.72</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>5000</v>
@@ -2913,7 +2913,7 @@
         <v>11843.32</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>11323.73</v>
+        <v>12403.64</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -3012,13 +3012,13 @@
         <v>2183</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3239.72</v>
+        <v>4319.63</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-1056.72</v>
+        <v>-2136.63</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.484067796610169</v>
+        <v>1.978758589097572</v>
       </c>
     </row>
     <row r="4">
@@ -3271,13 +3271,13 @@
         <v>35016.2</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>11323.73</v>
+        <v>12403.64</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>23692.47</v>
+        <v>22612.56</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.3233854615863514</v>
+        <v>0.3542257583632718</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1533,7 +1533,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1079.91</v>
+        <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0</v>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2 de 25</t>
+          <t>1 de 25</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2680,7 +2680,7 @@
         <v>7791.96</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1079.91</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>6000</v>
@@ -2913,7 +2913,7 @@
         <v>11843.32</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>12403.64</v>
+        <v>11323.73</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -3012,13 +3012,13 @@
         <v>2183</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4319.63</v>
+        <v>3239.72</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-2136.63</v>
+        <v>-1056.72</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.978758589097572</v>
+        <v>1.484067796610169</v>
       </c>
     </row>
     <row r="4">
@@ -3271,13 +3271,13 @@
         <v>35016.2</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>12403.64</v>
+        <v>11323.73</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>22612.56</v>
+        <v>23692.47</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.3542257583632718</v>
+        <v>0.3233854615863514</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0</v>
+        <v>-10114.14</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2159,7 +2159,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2815,7 +2815,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0</v>
+        <v>-10114.14</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>3000</v>
@@ -2913,7 +2913,7 @@
         <v>11843.32</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>11323.73</v>
+        <v>1209.59</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -2936,9 +2936,9 @@
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3228,13 +3228,13 @@
         <v>30623</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>7478.16</v>
+        <v>-2635.98</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>23144.84</v>
+        <v>33258.98</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.2442007641315351</v>
+        <v>-0.0860784377755282</v>
       </c>
     </row>
     <row r="13">
@@ -3271,13 +3271,13 @@
         <v>35016.2</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>11323.73</v>
+        <v>1209.59</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>23692.47</v>
+        <v>33806.61000000001</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.3233854615863514</v>
+        <v>0.03454372547563698</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>0</v>
+        <v>1133.57</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -1533,7 +1533,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
+        <v>1004.02</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>0</v>
+        <v>3534.56</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
@@ -2066,52 +2066,52 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
+          <t>2 de 25</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
           <t>1 de 25</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="L27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>1 de 25</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>3 de 25</t>
+          <t>5 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2572,7 +2572,7 @@
         <v>2916.85</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>1133.57</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>5000</v>
@@ -2680,7 +2680,7 @@
         <v>7791.96</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0</v>
+        <v>4538.58</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>6000</v>
@@ -2913,7 +2913,7 @@
         <v>11843.32</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>1209.59</v>
+        <v>6881.74</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -2936,9 +2936,9 @@
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3012,13 +3012,13 @@
         <v>2183</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3239.72</v>
+        <v>4243.74</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-1056.72</v>
+        <v>-2060.74</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.484067796610169</v>
+        <v>1.943994502977554</v>
       </c>
     </row>
     <row r="4">
@@ -3228,13 +3228,13 @@
         <v>30623</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>-2635.98</v>
+        <v>2032.15</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>33258.98</v>
+        <v>28590.85</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-0.0860784377755282</v>
+        <v>0.06636025209809621</v>
       </c>
     </row>
     <row r="13">
@@ -3271,13 +3271,13 @@
         <v>35016.2</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1209.59</v>
+        <v>6881.74</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>33806.61000000001</v>
+        <v>28134.46</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.03454372547563698</v>
+        <v>0.1965301774607182</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>0</v>
+        <v>6.91</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>5 de 25</t>
+          <t>6 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2734,7 +2734,7 @@
         <v>1047.1</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0</v>
+        <v>6.91</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>1500</v>
@@ -2913,7 +2913,7 @@
         <v>11843.32</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>6881.74</v>
+        <v>6888.650000000001</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -2938,7 +2938,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3228,13 +3228,13 @@
         <v>30623</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2032.15</v>
+        <v>2039.06</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>28590.85</v>
+        <v>28583.94</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.06636025209809621</v>
+        <v>0.06658589948731346</v>
       </c>
     </row>
     <row r="13">
@@ -3271,13 +3271,13 @@
         <v>35016.2</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6881.74</v>
+        <v>6888.65</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>28134.46</v>
+        <v>28127.55</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.1965301774607182</v>
+        <v>0.1967275146931991</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -780,7 +780,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2162.71</v>
+        <v>2185.77</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>0</v>
@@ -2302,7 +2302,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2162.71</v>
+        <v>2185.77</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>4000</v>
@@ -2913,7 +2913,7 @@
         <v>11843.32</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>6888.650000000001</v>
+        <v>6911.71</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -2938,7 +2938,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3228,13 +3228,13 @@
         <v>30623</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2039.06</v>
+        <v>2062.12</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>28583.94</v>
+        <v>28560.88</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.06658589948731346</v>
+        <v>0.0673389282565392</v>
       </c>
     </row>
     <row r="13">
@@ -3271,13 +3271,13 @@
         <v>35016.2</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6888.65</v>
+        <v>6911.71</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>28127.55</v>
+        <v>28104.49</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.1967275146931991</v>
+        <v>0.1973860670204077</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>8450.43</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>0</v>
+        <v>2358.59</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -1533,7 +1533,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1004.02</v>
+        <v>2083.93</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3534.56</v>
+        <v>6198.05</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>6 de 25</t>
+          <t>8 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2356,7 +2356,7 @@
         <v>-37.78</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>3239.72</v>
+        <v>11690.15</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>5000</v>
@@ -2518,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>605.85</v>
+        <v>2964.44</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>1000</v>
@@ -2680,7 +2680,7 @@
         <v>7791.96</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>4538.58</v>
+        <v>8281.98</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>6000</v>
@@ -2913,7 +2913,7 @@
         <v>11843.32</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>6911.71</v>
+        <v>21464.13</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -2936,7 +2936,7 @@
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3012,13 +3012,13 @@
         <v>2183</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4243.74</v>
+        <v>5323.65</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-2060.74</v>
+        <v>-3140.65</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.943994502977554</v>
+        <v>2.438685295464956</v>
       </c>
     </row>
     <row r="4">
@@ -3228,13 +3228,13 @@
         <v>30623</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2062.12</v>
+        <v>15534.63</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>28560.88</v>
+        <v>15088.37</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.0673389282565392</v>
+        <v>0.5072863533945073</v>
       </c>
     </row>
     <row r="13">
@@ -3271,13 +3271,13 @@
         <v>35016.2</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6911.71</v>
+        <v>21464.13</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>28104.49</v>
+        <v>13552.07</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.1973860670204077</v>
+        <v>0.6129771362969139</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -780,7 +780,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2185.77</v>
+        <v>3902.2</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>0</v>
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>0</v>
+        <v>6488.12</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>8 de 25</t>
+          <t>9 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2302,7 +2302,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2185.77</v>
+        <v>3902.2</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>4000</v>
@@ -2869,7 +2869,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0</v>
+        <v>6488.12</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>3500</v>
@@ -2913,7 +2913,7 @@
         <v>11843.32</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>21464.13</v>
+        <v>29668.68</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -3228,13 +3228,13 @@
         <v>30623</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>15534.63</v>
+        <v>23739.18</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>15088.37</v>
+        <v>6883.82</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.5072863533945073</v>
+        <v>0.7752075237566535</v>
       </c>
     </row>
     <row r="13">
@@ -3271,13 +3271,13 @@
         <v>35016.2</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>21464.13</v>
+        <v>29668.68</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>13552.07</v>
+        <v>5347.52</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.6129771362969139</v>
+        <v>0.8472843997920961</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>0</v>
+        <v>4636.23</v>
       </c>
       <c r="N16" s="2" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>6.91</v>
+        <v>1390.37</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
@@ -2037,10 +2037,10 @@
         <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>1938.62</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>0</v>
+        <v>9195.57</v>
       </c>
       <c r="N26" s="2" t="n">
         <v>0</v>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>0 de 25</t>
+          <t>1 de 25</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>9 de 25</t>
+          <t>11 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2653,7 +2653,7 @@
         <v>125.19</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0</v>
+        <v>4636.23</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>5000</v>
@@ -2734,7 +2734,7 @@
         <v>1047.1</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>6.91</v>
+        <v>1390.37</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>1500</v>
@@ -2896,7 +2896,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0</v>
+        <v>11134.19</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>5500</v>
@@ -2913,7 +2913,7 @@
         <v>11843.32</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>29668.68</v>
+        <v>46822.56</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -2937,8 +2937,8 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3204,13 +3204,13 @@
         <v>467</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>1938.62</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>467</v>
+        <v>-1471.62</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>4.151220556745182</v>
       </c>
     </row>
     <row r="12">
@@ -3228,13 +3228,13 @@
         <v>30623</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>23739.18</v>
+        <v>38954.44</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6883.82</v>
+        <v>-8331.440000000002</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.7752075237566535</v>
+        <v>1.272064787904516</v>
       </c>
     </row>
     <row r="13">
@@ -3271,13 +3271,13 @@
         <v>35016.2</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>29668.68</v>
+        <v>46822.56</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>5347.52</v>
+        <v>-11806.36</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8472843997920961</v>
+        <v>1.337168510575105</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -2653,7 +2653,7 @@
         <v>125.19</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>4636.23</v>
+        <v>4755.17</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>5000</v>
@@ -2913,7 +2913,7 @@
         <v>11843.32</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>46822.56</v>
+        <v>46941.5</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -3180,13 +3180,13 @@
         <v>115</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>118.94</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>115</v>
+        <v>-3.939999999999998</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>1.034260869565217</v>
       </c>
     </row>
     <row r="11">
@@ -3271,13 +3271,13 @@
         <v>35016.2</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>46822.56</v>
+        <v>46941.5</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-11806.36</v>
+        <v>-11925.3</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1.337168510575105</v>
+        <v>1.340565224096275</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -780,7 +780,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3902.2</v>
+        <v>0</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>0</v>
@@ -840,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1812.75</v>
+        <v>0</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>0</v>
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>3239.72</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0</v>
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>8450.43</v>
+        <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3502.7</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -1194,13 +1194,13 @@
         <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>605.85</v>
+        <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2358.59</v>
+        <v>0</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1133.57</v>
+        <v>0</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>4636.23</v>
+        <v>0</v>
       </c>
       <c r="N16" s="2" t="n">
         <v>0</v>
@@ -1533,7 +1533,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>2083.93</v>
+        <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>6198.05</v>
+        <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1390.37</v>
+        <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>-10114.14</v>
+        <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>6488.12</v>
+        <v>0</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
@@ -2037,10 +2037,10 @@
         <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1938.62</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>9195.57</v>
+        <v>0</v>
       </c>
       <c r="N26" s="2" t="n">
         <v>0</v>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2 de 25</t>
+          <t>0 de 25</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2101,17 +2101,17 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>1 de 25</t>
+          <t>0 de 25</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>1 de 25</t>
+          <t>0 de 25</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>11 de 25</t>
+          <t>0 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2156,10 +2156,10 @@
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2176,22 +2176,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2299,10 +2299,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>3902.2</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3902.2</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>4000</v>
@@ -2320,16 +2320,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>102.59</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>102.59</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>1812.75</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1812.75</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
@@ -2347,16 +2347,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>338.48</v>
+        <v>12910.91</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>12910.91</v>
+        <v>-37.78</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-37.78</v>
+        <v>11690.15</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>11690.15</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>5000</v>
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>3231.36</v>
+        <v>0</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>3502.7</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>3502.7</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>3000</v>
@@ -2515,10 +2515,10 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>2964.44</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>2964.44</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>1000</v>
@@ -2563,16 +2563,16 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0</v>
+        <v>10650.37</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>10650.37</v>
+        <v>2916.85</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2916.85</v>
+        <v>1133.57</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1133.57</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>5000</v>
@@ -2644,16 +2644,16 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>2356.99</v>
+        <v>6938.84</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>6938.84</v>
+        <v>125.19</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>125.19</v>
+        <v>4755.17</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>4755.17</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>5000</v>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0</v>
+        <v>15134.51</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>15134.51</v>
+        <v>7791.96</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>7791.96</v>
+        <v>8281.98</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>8281.98</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>6000</v>
@@ -2725,16 +2725,16 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0</v>
+        <v>2392.08</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2392.08</v>
+        <v>1047.1</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1047.1</v>
+        <v>1390.37</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1390.37</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>1500</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-122.43</v>
+        <v>0</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0</v>
@@ -2806,16 +2806,16 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>718.15</v>
+        <v>10114.14</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>10114.14</v>
+        <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0</v>
+        <v>-10114.14</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-10114.14</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>3000</v>
@@ -2866,10 +2866,10 @@
         <v>0</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0</v>
+        <v>6488.12</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>6488.12</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>3500</v>
@@ -2887,16 +2887,16 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>-23.39</v>
+        <v>0</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0</v>
+        <v>11134.19</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>11134.19</v>
+        <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>5500</v>
@@ -2904,16 +2904,16 @@
     </row>
     <row r="28">
       <c r="C28" s="6" t="n">
-        <v>6499.16</v>
+        <v>58243.44</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>58243.44</v>
+        <v>11843.32</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>11843.32</v>
+        <v>46941.5</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>46941.5</v>
+        <v>0</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -780,7 +780,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0</v>
+        <v>1805.64</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>0</v>
@@ -1233,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>649.96</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>0</v>
+        <v>3293.72</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -2066,52 +2066,52 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
+          <t>1 de 25</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="L27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>0 de 25</t>
+          <t>2 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2159,7 +2159,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2302,7 +2302,7 @@
         <v>3902.2</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0</v>
+        <v>1805.64</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>4000</v>
@@ -2572,7 +2572,7 @@
         <v>1133.57</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>3943.68</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>5000</v>
@@ -2913,7 +2913,7 @@
         <v>46941.5</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0</v>
+        <v>5749.32</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>0</v>
+        <v>1464.57</v>
       </c>
       <c r="N16" s="2" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>2 de 25</t>
+          <t>3 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2653,7 +2653,7 @@
         <v>4755.17</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0</v>
+        <v>1464.57</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>5000</v>
@@ -2913,7 +2913,7 @@
         <v>46941.5</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>5749.32</v>
+        <v>7213.889999999999</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -2930,15 +2930,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3012,13 +3012,13 @@
         <v>2183</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>5323.65</v>
+        <v>649.96</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-3140.65</v>
+        <v>1533.04</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.438685295464956</v>
+        <v>0.2977370590929913</v>
       </c>
     </row>
     <row r="4">
@@ -3057,13 +3057,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>172.82</v>
+        <v>198.5</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>172.82</v>
+        <v>198.5</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -3077,17 +3077,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LAVABOS</t>
+          <t>INODOROS</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>263</v>
+        <v>5190</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>263</v>
+        <v>5190</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
@@ -3101,17 +3101,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NO RESURTIBLES</t>
+          <t>LAVABOS</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>250</v>
+        <v>963</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>250</v>
+        <v>963</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -3125,17 +3125,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OTROS</t>
+          <t>NO RESURTIBLES</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -3149,20 +3149,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PANELES DECORATIVOS</t>
+          <t>OTROS</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>407</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>605.85</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-198.85</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.488574938574939</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -3173,20 +3173,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PANELES PVC Y PU</t>
+          <t>PANELES DECORATIVOS</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>115</v>
+        <v>407</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>118.94</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-3.939999999999998</v>
+        <v>407</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.034260869565217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -3197,20 +3197,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PIEDRA SINTERIZADA</t>
+          <t>PANELES PVC Y PU</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>467</v>
+        <v>115</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1938.62</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-1471.62</v>
+        <v>115</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>4.151220556745182</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3221,20 +3221,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PORCELANATO</t>
+          <t>PIEDRA SINTERIZADA</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>30623</v>
+        <v>1467</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>38954.44</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-8331.440000000002</v>
+        <v>1467</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1.272064787904516</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3245,39 +3245,63 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>PORCELANATO</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>32623</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>6563.93</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>26059.07</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0.20120559114735</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>PUERTAS DE SEGURIDAD</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C14" s="2" t="n">
         <v>199.8</v>
       </c>
-      <c r="D13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2" t="n">
+      <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="n">
         <v>199.8</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>35016.2</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>46941.5</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>-11925.3</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>1.340565224096275</v>
+      <c r="C15" s="2" t="n">
+        <v>43931.88</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>7213.89</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>36717.99000000001</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.164206266610944</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>0</v>
+        <v>28.12</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>3 de 25</t>
+          <t>4 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2680,7 +2680,7 @@
         <v>8281.98</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0</v>
+        <v>28.12</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>6000</v>
@@ -2913,7 +2913,7 @@
         <v>46941.5</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>7213.889999999999</v>
+        <v>7242.01</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -3252,13 +3252,13 @@
         <v>32623</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6563.93</v>
+        <v>6592.05</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>26059.07</v>
+        <v>26030.95</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.20120559114735</v>
+        <v>0.2020675596971462</v>
       </c>
     </row>
     <row r="14">
@@ -3295,13 +3295,13 @@
         <v>43931.88</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>7213.89</v>
+        <v>7242.01</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>36717.99000000001</v>
+        <v>36689.87</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.164206266610944</v>
+        <v>0.1648463484831516</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0</v>
+        <v>12131.73</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>4 de 25</t>
+          <t>5 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2159,7 +2159,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2761,7 +2761,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0</v>
+        <v>12131.73</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>5000</v>
@@ -2913,7 +2913,7 @@
         <v>46941.5</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>7242.01</v>
+        <v>19373.74</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -2936,7 +2936,7 @@
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3252,13 +3252,13 @@
         <v>32623</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6592.05</v>
+        <v>18723.78</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>26030.95</v>
+        <v>13899.22</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.2020675596971462</v>
+        <v>0.57394414983294</v>
       </c>
     </row>
     <row r="14">
@@ -3295,13 +3295,13 @@
         <v>43931.88</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>7242.01</v>
+        <v>19373.74</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>36689.87</v>
+        <v>24558.14</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.1648463484831516</v>
+        <v>0.4409950131886001</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3293.72</v>
+        <v>5180.61</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -2572,7 +2572,7 @@
         <v>1133.57</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>3943.68</v>
+        <v>5830.57</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>5000</v>
@@ -2913,7 +2913,7 @@
         <v>46941.5</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>19373.74</v>
+        <v>21260.63</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -3252,13 +3252,13 @@
         <v>32623</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>18723.78</v>
+        <v>20610.67</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>13899.22</v>
+        <v>12012.33</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.57394414983294</v>
+        <v>0.6317834043466266</v>
       </c>
     </row>
     <row r="14">
@@ -3295,13 +3295,13 @@
         <v>43931.88</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>19373.74</v>
+        <v>21260.63</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>24558.14</v>
+        <v>22671.25</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.4409950131886001</v>
+        <v>0.4839453717892336</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1464.57</v>
+        <v>2495.09</v>
       </c>
       <c r="N16" s="2" t="n">
         <v>0</v>
@@ -2653,7 +2653,7 @@
         <v>4755.17</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1464.57</v>
+        <v>2495.09</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>5000</v>
@@ -2913,7 +2913,7 @@
         <v>46941.5</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>21260.63</v>
+        <v>22291.15</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -3252,13 +3252,13 @@
         <v>32623</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>20610.67</v>
+        <v>21641.19</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>12012.33</v>
+        <v>10981.81</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.6317834043466266</v>
+        <v>0.6633721607454863</v>
       </c>
     </row>
     <row r="14">
@@ -3295,13 +3295,13 @@
         <v>43931.88</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>21260.63</v>
+        <v>22291.15</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>22671.25</v>
+        <v>21640.73</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.4839453717892336</v>
+        <v>0.50740259692961</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -780,7 +780,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1805.64</v>
+        <v>3673.74</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>5180.61</v>
+        <v>5956.77</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -2302,7 +2302,7 @@
         <v>3902.2</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1805.64</v>
+        <v>3673.74</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>4000</v>
@@ -2572,7 +2572,7 @@
         <v>1133.57</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>5830.57</v>
+        <v>6606.73</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>5000</v>
@@ -2913,7 +2913,7 @@
         <v>46941.5</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>22291.15</v>
+        <v>24935.41</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -3252,13 +3252,13 @@
         <v>32623</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>21641.19</v>
+        <v>24285.45</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>10981.81</v>
+        <v>8337.549999999999</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.6633721607454863</v>
+        <v>0.7444272445820433</v>
       </c>
     </row>
     <row r="14">
@@ -3295,13 +3295,13 @@
         <v>43931.88</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>22291.15</v>
+        <v>24935.41</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>21640.73</v>
+        <v>18996.47</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.50740259692961</v>
+        <v>0.5675926001800969</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>51.92</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>5 de 25</t>
+          <t>6 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2356,7 +2356,7 @@
         <v>11690.15</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
+        <v>51.92</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>5000</v>
@@ -2913,7 +2913,7 @@
         <v>46941.5</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>24935.41</v>
+        <v>24987.33</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -2937,7 +2937,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -3252,13 +3252,13 @@
         <v>32623</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>24285.45</v>
+        <v>24337.37</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>8337.549999999999</v>
+        <v>8285.630000000001</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.7444272445820433</v>
+        <v>0.7460187597707139</v>
       </c>
     </row>
     <row r="14">
@@ -3295,13 +3295,13 @@
         <v>43931.88</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>24935.41</v>
+        <v>24987.33</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>18996.47</v>
+        <v>18944.55</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.5675926001800969</v>
+        <v>0.5687744298673308</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -2653,7 +2653,7 @@
         <v>4755.17</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>2495.09</v>
+        <v>2376.15</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>5000</v>
@@ -2913,7 +2913,7 @@
         <v>46941.5</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>24987.33</v>
+        <v>24868.39</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -3204,13 +3204,13 @@
         <v>115</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>-118.94</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>115</v>
+        <v>233.94</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>-1.034260869565217</v>
       </c>
     </row>
     <row r="12">
@@ -3295,13 +3295,13 @@
         <v>43931.88</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>24987.33</v>
+        <v>24868.39</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>18944.55</v>
+        <v>19063.49</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.5687744298673308</v>
+        <v>0.5660670565429933</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>313.06</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
@@ -777,7 +777,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>860.8099999999999</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>3673.74</v>
@@ -2066,47 +2066,47 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
+          <t>2 de 25</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
           <t>1 de 25</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
@@ -2302,7 +2302,7 @@
         <v>3902.2</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3673.74</v>
+        <v>4847.61</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>4000</v>
@@ -2913,7 +2913,7 @@
         <v>46941.5</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>24868.39</v>
+        <v>26042.26</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -3012,13 +3012,13 @@
         <v>2183</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>649.96</v>
+        <v>963.02</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1533.04</v>
+        <v>1219.98</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.2977370590929913</v>
+        <v>0.4411452130096198</v>
       </c>
     </row>
     <row r="4">
@@ -3228,13 +3228,13 @@
         <v>1467</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>860.8099999999999</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1467</v>
+        <v>606.1900000000001</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.5867825494205862</v>
       </c>
     </row>
     <row r="13">
@@ -3295,13 +3295,13 @@
         <v>43931.88</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>24868.39</v>
+        <v>26042.26</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>19063.49</v>
+        <v>17889.62</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.5660670565429933</v>
+        <v>0.5927872879558078</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>677.21</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>28.12</v>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>1 de 25</t>
+          <t>2 de 25</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
@@ -2680,7 +2680,7 @@
         <v>8281.98</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>28.12</v>
+        <v>705.33</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>6000</v>
@@ -2913,7 +2913,7 @@
         <v>46941.5</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>26042.26</v>
+        <v>26719.47</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -2937,7 +2937,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -3228,13 +3228,13 @@
         <v>1467</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>860.8099999999999</v>
+        <v>1538.02</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>606.1900000000001</v>
+        <v>-71.01999999999998</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.5867825494205862</v>
+        <v>1.048411724608044</v>
       </c>
     </row>
     <row r="13">
@@ -3295,13 +3295,13 @@
         <v>43931.88</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>26042.26</v>
+        <v>26719.47</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>17889.62</v>
+        <v>17212.41</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.5927872879558078</v>
+        <v>0.6082022895446313</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R27"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FERNANDEZ CEVALLOS JUAN CARLOS</t>
+          <t>FERRETERIAS FERRIGONZ SA</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -1166,14 +1166,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FERRETERIAS FERRIGONZ SA</t>
+          <t>JARAMILLO CARVAJAL NICOLAS ESTEBAN</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>649.96</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>0</v>
+        <v>5956.77</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -1226,14 +1226,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JARAMILLO CARVAJAL NICOLAS ESTEBAN</t>
+          <t>MARIN DELGADO BRENDA MARIA</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>649.96</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>5956.77</v>
+        <v>0</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MARIN DELGADO BRENDA MARIA</t>
+          <t>MATERIALES DE CONSTRUCCION SUPERMACONSVI S.A.</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MATERIALES DE CONSTRUCCION SUPERMACONSVI S.A.</t>
+          <t>MEGAMAFERS S.A.</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0</v>
+        <v>2495.09</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MEGAMAFERS S.A.</t>
+          <t>MORILLO CORRAL RUBI KATERINE</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2495.09</v>
+        <v>0</v>
       </c>
       <c r="N16" s="2" t="n">
         <v>0</v>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MORILLO CORRAL RUBI KATERINE</t>
+          <t>MUÑOZ LOZA ROMMEL SEBASTIAN</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -1497,10 +1497,10 @@
         <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>677.21</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0</v>
+        <v>28.12</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MUÑOZ LOZA ROMMEL SEBASTIAN</t>
+          <t>ORTEGA PAREDES RUDHT ELENA</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -1557,10 +1557,10 @@
         <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>677.21</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>28.12</v>
+        <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ORTEGA PAREDES RUDHT ELENA</t>
+          <t>OÑATE PEREZ MERCY YOLANDA</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OÑATE PEREZ MERCY YOLANDA</t>
+          <t>PADILLA MIER BERTHA MARIETA</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>0</v>
+        <v>12131.73</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PADILLA MIER BERTHA MARIETA</t>
+          <t>PAVIMARSA S.A.</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>12131.73</v>
+        <v>0</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PAVIMARSA S.A.</t>
+          <t>SARZOSA UNDA JOSE DOMINGO</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SARZOSA UNDA JOSE DOMINGO</t>
+          <t>SIGCHOS MORA FRANKLIN PORFIRIO</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SIGCHOS MORA FRANKLIN PORFIRIO</t>
+          <t>TRUJILLO TORRES VINICIO RUBEN</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TRUJILLO TORRES VINICIO RUBEN</t>
+          <t>TULCAN NARVAEZ EDITH MARITZA</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -1999,144 +1999,84 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>TULCAN NARVAEZ EDITH MARITZA</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>2 de 25</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>2 de 25</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr">
-        <is>
-          <t>6 de 25</t>
-        </is>
-      </c>
-      <c r="N27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="O27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="P27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="Q27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="R27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>2 de 24</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>2 de 24</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>6 de 24</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
+        </is>
+      </c>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
+        </is>
+      </c>
+      <c r="P26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
+        </is>
+      </c>
+      <c r="R26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
         </is>
       </c>
     </row>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -2870,7 +2870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -3017,17 +3017,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INODOROS</t>
+          <t>LAVABOS</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>5190</v>
+        <v>963</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>5190</v>
+        <v>963</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
@@ -3041,17 +3041,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LAVABOS</t>
+          <t>NO RESURTIBLES</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>963</v>
+        <v>250</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>963</v>
+        <v>250</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -3065,17 +3065,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NO RESURTIBLES</t>
+          <t>OTROS</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -3089,17 +3089,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OTROS</t>
+          <t>PANELES DECORATIVOS</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0</v>
+        <v>407</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>407</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -3113,20 +3113,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PANELES DECORATIVOS</t>
+          <t>PANELES PVC Y PU</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>407</v>
+        <v>115</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>-118.94</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>407</v>
+        <v>233.94</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>-1.034260869565217</v>
       </c>
     </row>
     <row r="11">
@@ -3137,20 +3137,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PANELES PVC Y PU</t>
+          <t>PIEDRA SINTERIZADA</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>115</v>
+        <v>1467</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>-118.94</v>
+        <v>1538.02</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>233.94</v>
+        <v>-71.01999999999998</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-1.034260869565217</v>
+        <v>1.048411724608044</v>
       </c>
     </row>
     <row r="12">
@@ -3161,20 +3161,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PIEDRA SINTERIZADA</t>
+          <t>PORCELANATO</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1467</v>
+        <v>32623</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1538.02</v>
+        <v>24337.37</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-71.01999999999998</v>
+        <v>8285.630000000001</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1.048411724608044</v>
+        <v>0.7460187597707139</v>
       </c>
     </row>
     <row r="13">
@@ -3185,63 +3185,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PORCELANATO</t>
+          <t>PUERTAS DE SEGURIDAD</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>32623</v>
+        <v>199.8</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>24337.37</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>8285.630000000001</v>
+        <v>199.8</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.7460187597707139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>PUERTAS DE SEGURIDAD</t>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>199.8</v>
+        <v>38741.88</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>26719.47</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>199.8</v>
+        <v>12022.41</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>43931.88</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>26719.47</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>17212.41</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>0.6082022895446313</v>
+        <v>0.6896792308478575</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -894,13 +894,13 @@
         <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>409.46</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>51.92</v>
+        <v>2720.64</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>2393.76</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>677.21</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>28.12</v>
+        <v>2595.75</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>0 de 24</t>
+          <t>1 de 24</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>6 de 24</t>
+          <t>7 de 24</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2296,7 +2296,7 @@
         <v>11690.15</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>51.92</v>
+        <v>3130.1</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>5000</v>
@@ -2377,7 +2377,7 @@
         <v>3502.7</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
+        <v>2393.76</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>3000</v>
@@ -2620,7 +2620,7 @@
         <v>8281.98</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>705.33</v>
+        <v>3272.96</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>6000</v>
@@ -2853,7 +2853,7 @@
         <v>46941.5</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>26719.47</v>
+        <v>34759.04</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -3096,13 +3096,13 @@
         <v>407</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>409.46</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>407</v>
+        <v>-2.45999999999998</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>1.006044226044226</v>
       </c>
     </row>
     <row r="10">
@@ -3168,13 +3168,13 @@
         <v>32623</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>24337.37</v>
+        <v>31967.48</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>8285.630000000001</v>
+        <v>655.5200000000004</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.7460187597707139</v>
+        <v>0.9799062011464305</v>
       </c>
     </row>
     <row r="13">
@@ -3211,13 +3211,13 @@
         <v>38741.88</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>26719.47</v>
+        <v>34759.04</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>12022.41</v>
+        <v>3982.840000000001</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.6896792308478575</v>
+        <v>0.897195489738753</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1500,7 +1500,7 @@
         <v>677.21</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2595.75</v>
+        <v>2575.53</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -2620,7 +2620,7 @@
         <v>8281.98</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>3272.96</v>
+        <v>3252.74</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>6000</v>
@@ -2853,7 +2853,7 @@
         <v>46941.5</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>34759.04</v>
+        <v>34738.82</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -3168,13 +3168,13 @@
         <v>32623</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>31967.48</v>
+        <v>31947.26</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>655.5200000000004</v>
+        <v>675.7400000000016</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.9799062011464305</v>
+        <v>0.9792863930355883</v>
       </c>
     </row>
     <row r="13">
@@ -3211,13 +3211,13 @@
         <v>38741.88</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>34759.04</v>
+        <v>34738.82</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>3982.840000000001</v>
+        <v>4003.060000000002</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.897195489738753</v>
+        <v>0.896673573920522</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2720.64</v>
+        <v>7870.44</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>11690.15</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>3130.1</v>
+        <v>8279.9</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>5000</v>
@@ -2853,7 +2853,7 @@
         <v>46941.5</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>34738.82</v>
+        <v>39888.62</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>
@@ -3168,13 +3168,13 @@
         <v>32623</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>31947.26</v>
+        <v>37097.06</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>675.7400000000016</v>
+        <v>-4474.059999999998</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.9792863930355883</v>
+        <v>1.137144346013549</v>
       </c>
     </row>
     <row r="13">
@@ -3211,13 +3211,13 @@
         <v>38741.88</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>34738.82</v>
+        <v>39888.62</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>4003.060000000002</v>
+        <v>-1146.739999999998</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.896673573920522</v>
+        <v>1.029599492848566</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>313.06</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>860.8099999999999</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3673.74</v>
+        <v>0</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>0</v>
@@ -894,13 +894,13 @@
         <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>409.46</v>
+        <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>7870.44</v>
+        <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2393.76</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>649.96</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>5956.77</v>
+        <v>0</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2495.09</v>
+        <v>0</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -1497,10 +1497,10 @@
         <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>677.21</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2575.53</v>
+        <v>0</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>12131.73</v>
+        <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2 de 24</t>
+          <t>0 de 24</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -2041,17 +2041,17 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>1 de 24</t>
+          <t>0 de 24</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>2 de 24</t>
+          <t>0 de 24</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>7 de 24</t>
+          <t>0 de 24</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2096,10 +2096,10 @@
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2116,22 +2116,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2236,13 +2236,13 @@
         <v>0</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>3902.2</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3902.2</v>
+        <v>4847.61</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>4847.61</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>4000</v>
@@ -2260,13 +2260,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>102.59</v>
+        <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>1812.75</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1812.75</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -2287,16 +2287,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>12910.91</v>
+        <v>-37.78</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-37.78</v>
+        <v>11690.15</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>11690.15</v>
+        <v>8279.9</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>8279.9</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>5000</v>
@@ -2371,13 +2371,13 @@
         <v>0</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>3502.7</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>3502.7</v>
+        <v>2393.76</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2393.76</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>3000</v>
@@ -2452,10 +2452,10 @@
         <v>0</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>2964.44</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2964.44</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>10650.37</v>
+        <v>2916.85</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>2916.85</v>
+        <v>1133.57</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1133.57</v>
+        <v>6827.71</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>6606.73</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>5000</v>
@@ -2584,16 +2584,16 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>6938.84</v>
+        <v>125.19</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>125.19</v>
+        <v>4755.17</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>4755.17</v>
+        <v>5886.02</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>2376.15</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>5000</v>
@@ -2611,16 +2611,16 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>15134.51</v>
+        <v>7791.96</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>7791.96</v>
+        <v>8281.98</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>8281.98</v>
+        <v>3252.74</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>3252.74</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>6000</v>
@@ -2665,13 +2665,13 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>2392.08</v>
+        <v>1047.1</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1047.1</v>
+        <v>1390.37</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1390.37</v>
+        <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>0</v>
@@ -2698,10 +2698,10 @@
         <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>12131.73</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>12131.73</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>5000</v>
@@ -2746,13 +2746,13 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>10114.14</v>
+        <v>0</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0</v>
+        <v>-10114.14</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-10114.14</v>
+        <v>0</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0</v>
+        <v>6488.12</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>6488.12</v>
+        <v>0</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0</v>
@@ -2830,10 +2830,10 @@
         <v>0</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0</v>
+        <v>11134.19</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>11134.19</v>
+        <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>0</v>
@@ -2844,16 +2844,16 @@
     </row>
     <row r="28">
       <c r="C28" s="6" t="n">
-        <v>58243.44</v>
+        <v>11843.32</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>11843.32</v>
+        <v>46941.5</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>46941.5</v>
+        <v>43619.47</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>39888.62</v>
+        <v>0</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>48500</v>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -2191,7 +2191,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2299,7 +2299,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>5000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="8">
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="14">
@@ -2650,7 +2650,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="21">
@@ -2704,7 +2704,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="23">
@@ -2758,7 +2758,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>3500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="27">
@@ -2839,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>5500</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="28">
@@ -2856,7 +2856,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>48500</v>
+        <v>45500</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -2091,11 +2091,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ANDINO RENDON ARACELY</t>
+          <t>BENAVIDES REVELO SILVIA PATRICIA</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -2175,23 +2175,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BENAVIDES REVELO SILVIA PATRICIA</t>
+          <t>CARRION CARRION LESLY ANABE</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>3902.2</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>4847.61</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="4">
@@ -2202,14 +2202,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BENITEZ ANGAMARCA RICHARD EDISON</t>
+          <t>CARRION CARRION STEPHANIE DAYANA</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>1812.75</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
@@ -2229,23 +2229,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CARRION CARRION LESLY ANABE</t>
+          <t>CHASIQUIZA CAMPAÑA JOSE LUIS</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0</v>
+        <v>-37.78</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>3902.2</v>
+        <v>11690.15</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4847.61</v>
+        <v>8279.9</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>4000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="6">
@@ -2256,14 +2256,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CARRION CARRION STEPHANIE DAYANA</t>
+          <t>CHONTASI SIMBAÑA SILVIA JANETH</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1812.75</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
@@ -2283,23 +2283,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CHASIQUIZA CAMPAÑA JOSE LUIS</t>
+          <t>DECORHOME S.C.C.</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-37.78</v>
+        <v>0</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>11690.15</v>
+        <v>3502.7</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>8279.9</v>
+        <v>2393.76</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="8">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CHAVEZ IMBAQUINGO EDGAR MAURICIO</t>
+          <t>ESCUDERO CRUZ SILVIA RAQUEL</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CHONTASI SIMBAÑA SILVIA JANETH</t>
+          <t>FERNANDEZ CEVALLOS JUAN CARLOS</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -2364,23 +2364,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DECORHOME S.C.C.</t>
+          <t>FERRETERIAS FERRIGONZ SA</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>3502.7</v>
+        <v>2964.44</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2393.76</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="11">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ESCUDERO CRUZ SILVIA RAQUEL</t>
+          <t>IMPORTADORA VEGA S.A.</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -2418,23 +2418,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FERNANDEZ CEVALLOS JUAN CARLOS</t>
+          <t>JARAMILLO CARVAJAL NICOLAS ESTEBAN</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0</v>
+        <v>2916.85</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>1133.57</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>6827.71</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="13">
@@ -2445,14 +2445,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FERRETERIAS FERRIGONZ SA</t>
+          <t>MARIN DELGADO BRENDA MARIA</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>2964.44</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2472,23 +2472,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IMPORTADORA VEGA S.A.</t>
+          <t>MEGAMAFERS S.A.</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0</v>
+        <v>125.19</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>4755.17</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>5886.02</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="15">
@@ -2499,23 +2499,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JARAMILLO CARVAJAL NICOLAS ESTEBAN</t>
+          <t>MUÑOZ LOZA ROMMEL SEBASTIAN</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>2916.85</v>
+        <v>7791.96</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1133.57</v>
+        <v>8281.98</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>6827.71</v>
+        <v>3252.74</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>5000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="16">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MARIN DELGADO BRENDA MARIA</t>
+          <t>ORTEGA PAREDES RUDHT ELENA</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -2542,7 +2542,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="17">
@@ -2553,14 +2553,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MATERIALES DE CONSTRUCCION SUPERMACONSVI S.A.</t>
+          <t>OÑATE PEREZ MERCY YOLANDA</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0</v>
+        <v>1047.1</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0</v>
+        <v>1390.37</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>0</v>
@@ -2569,7 +2569,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="18">
@@ -2580,23 +2580,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MEGAMAFERS S.A.</t>
+          <t>PADILLA MIER BERTHA MARIETA</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>125.19</v>
+        <v>0</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>4755.17</v>
+        <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>5886.02</v>
+        <v>12131.73</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="19">
@@ -2607,23 +2607,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MUÑOZ LOZA ROMMEL SEBASTIAN</t>
+          <t>SARZOSA UNDA JOSE DOMINGO</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>7791.96</v>
+        <v>0</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>8281.98</v>
+        <v>-10114.14</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>3252.74</v>
+        <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ORTEGA PAREDES RUDHT ELENA</t>
+          <t>SIGCHOS MORA FRANKLIN PORFIRIO</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -2650,7 +2650,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2661,14 +2661,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>OÑATE PEREZ MERCY YOLANDA</t>
+          <t>TRUJILLO TORRES VINICIO RUBEN</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1047.1</v>
+        <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1390.37</v>
+        <v>6488.12</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0</v>
@@ -2677,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="22">
@@ -2688,174 +2688,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PADILLA MIER BERTHA MARIETA</t>
+          <t>TULCAN NARVAEZ EDITH MARITZA</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>11134.19</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>12131.73</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>PAVIMARSA S.A.</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>SARZOSA UNDA JOSE DOMINGO</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>-10114.14</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>SIGCHOS MORA FRANKLIN PORFIRIO</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>TRUJILLO TORRES VINICIO RUBEN</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>6488.12</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>TULCAN NARVAEZ EDITH MARITZA</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>11134.19</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28" s="6" t="n">
+      <c r="C23" s="6" t="n">
         <v>11843.32</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D23" s="6" t="n">
         <v>46941.5</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E23" s="6" t="n">
         <v>43619.47</v>
       </c>
-      <c r="F28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="6" t="n">
+      <c r="F23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="6" t="n">
         <v>45500</v>
       </c>
     </row>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0</v>
+        <v>-139.09</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
@@ -2485,7 +2485,7 @@
         <v>5886.02</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0</v>
+        <v>-139.09</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>5000</v>
@@ -2718,7 +2718,7 @@
         <v>43619.47</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0</v>
+        <v>-139.09</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>45500</v>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -2735,15 +2735,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2817,13 +2817,13 @@
         <v>2183</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>963.02</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1219.98</v>
+        <v>2183</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.4411452130096198</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2834,17 +2834,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FREGADEROS DE COCINA</t>
+          <t>CERAMICA</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>199.5</v>
+        <v>3732</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>199.5</v>
+        <v>3732</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
@@ -2858,20 +2858,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GRIFERIAS</t>
+          <t>FREGADEROS DE COCINA</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>198.5</v>
+        <v>199.5</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>-139.09</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>198.5</v>
+        <v>338.59</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0</v>
+        <v>-0.6971929824561404</v>
       </c>
     </row>
     <row r="6">
@@ -2882,17 +2882,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LAVABOS</t>
+          <t>GRIFERIAS</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>963</v>
+        <v>198.5</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>963</v>
+        <v>198.5</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
@@ -2906,17 +2906,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NO RESURTIBLES</t>
+          <t>INODOROS</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>250</v>
+        <v>5190</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>250</v>
+        <v>5190</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -2930,17 +2930,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OTROS</t>
+          <t>LAVABOS</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0</v>
+        <v>963</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>963</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -2954,20 +2954,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PANELES DECORATIVOS</t>
+          <t>NO RESURTIBLES</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>407</v>
+        <v>250</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>409.46</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-2.45999999999998</v>
+        <v>250</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.006044226044226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2978,20 +2978,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PANELES PVC Y PU</t>
+          <t>OTROS</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>-118.94</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>233.94</v>
+        <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-1.034260869565217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -3002,20 +3002,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PIEDRA SINTERIZADA</t>
+          <t>PANELES DECORATIVOS</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1467</v>
+        <v>407</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1538.02</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-71.01999999999998</v>
+        <v>407</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.048411724608044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3026,20 +3026,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PORCELANATO</t>
+          <t>PANELES PVC Y PU</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>32623</v>
+        <v>115</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>37097.06</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-4474.059999999998</v>
+        <v>115</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1.137144346013549</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3050,39 +3050,87 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>PIEDRA SINTERIZADA</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>1467</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PORCELANATO</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>36556</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>36556</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>PUERTAS DE SEGURIDAD</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C15" s="2" t="n">
         <v>199.8</v>
       </c>
-      <c r="D13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2" t="n">
+      <c r="D15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2" t="n">
         <v>199.8</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>38741.88</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>39888.62</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>-1146.739999999998</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>1.029599492848566</v>
+      <c r="C16" s="2" t="n">
+        <v>51596.88</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>-139.09</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>51735.97</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-0.002695705631813396</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -960,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0</v>
+        <v>2468.57</v>
       </c>
       <c r="N8" s="2" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0</v>
+        <v>1550.24</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1605,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0</v>
+        <v>2801.71</v>
       </c>
       <c r="I19" s="2" t="n">
         <v>0</v>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
+          <t>1 de 24</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
           <t>0 de 24</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>0 de 24</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>0 de 24</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>0 de 24</t>
         </is>
       </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>0 de 24</t>
+          <t>2 de 24</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0</v>
+        <v>2468.57</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
@@ -2512,7 +2512,7 @@
         <v>3252.74</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>1550.24</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>6000</v>
@@ -2566,7 +2566,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0</v>
+        <v>2801.71</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>1500</v>
@@ -2718,7 +2718,7 @@
         <v>43619.47</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>-139.09</v>
+        <v>6681.43</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>45500</v>
@@ -2913,13 +2913,13 @@
         <v>5190</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>2801.71</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>5190</v>
+        <v>2388.29</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>0.5398285163776493</v>
       </c>
     </row>
     <row r="8">
@@ -3081,13 +3081,13 @@
         <v>36556</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>4018.81</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>36556</v>
+        <v>32537.19</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0</v>
+        <v>0.109935715067294</v>
       </c>
     </row>
     <row r="15">
@@ -3124,13 +3124,13 @@
         <v>51596.88</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>-139.09</v>
+        <v>6681.43</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>51735.97</v>
+        <v>44915.45</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.002695705631813396</v>
+        <v>0.1294929073230784</v>
       </c>
     </row>
   </sheetData>
